--- a/analysis_outputs_r/R_Analysis_Summary.xlsx
+++ b/analysis_outputs_r/R_Analysis_Summary.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="524">
   <si>
     <t xml:space="preserve">Sheet</t>
   </si>
@@ -296,6 +296,9 @@
     <t xml:space="preserve">Fisherman</t>
   </si>
   <si>
+    <t xml:space="preserve">Other</t>
+  </si>
+  <si>
     <t xml:space="preserve">Source location</t>
   </si>
   <si>
@@ -308,21 +311,18 @@
     <t xml:space="preserve">Bhola charter landing</t>
   </si>
   <si>
+    <t xml:space="preserve">Teknaf</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kuakata</t>
   </si>
   <si>
-    <t xml:space="preserve">Teknaf</t>
-  </si>
-  <si>
     <t xml:space="preserve">Moheshkhali</t>
   </si>
   <si>
     <t xml:space="preserve">Kutubdia</t>
   </si>
   <si>
-    <t xml:space="preserve">Cox's Bazar landing</t>
-  </si>
-  <si>
     <t xml:space="preserve">Credit sales share</t>
   </si>
   <si>
@@ -341,21 +341,18 @@
     <t xml:space="preserve">Buys from</t>
   </si>
   <si>
-    <t xml:space="preserve">Other</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sells to</t>
   </si>
   <si>
     <t xml:space="preserve">Household</t>
   </si>
   <si>
+    <t xml:space="preserve">Hotel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hawker</t>
   </si>
   <si>
-    <t xml:space="preserve">Hotel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Institutional</t>
   </si>
   <si>
@@ -446,6 +443,9 @@
     <t xml:space="preserve">Indian salmon (four-finger threadfin)</t>
   </si>
   <si>
+    <t xml:space="preserve">Descriptive-only (Method 3.8): consumer quotes n=1 (&lt;3; share not reported)</t>
+  </si>
+  <si>
     <t xml:space="preserve">S04</t>
   </si>
   <si>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">Thorny/Indian anchovy</t>
   </si>
   <si>
-    <t xml:space="preserve">Descriptive-only (Method 3.8): retail quotes in 2 market(s); consumer quotes n=1 (&lt;3; share not reported)</t>
+    <t xml:space="preserve">Descriptive-only (Method 3.8): retail quotes in 1 market(s); consumer quotes n=1 (&lt;3; share not reported)</t>
   </si>
   <si>
     <t xml:space="preserve">S09</t>
@@ -503,31 +503,31 @@
     <t xml:space="preserve">Bombay duck</t>
   </si>
   <si>
+    <t xml:space="preserve">Descriptive-only (Method 3.8): retail quotes in 1 market(s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chacunda gizzard shad</t>
+  </si>
+  <si>
     <t xml:space="preserve">Descriptive-only (Method 3.8): retail quotes in 2 market(s)</t>
   </si>
   <si>
-    <t xml:space="preserve">S10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chacunda gizzard shad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descriptive-only (Method 3.8): retail quotes in 1 market(s); consumer quotes n=1 (&lt;3; share not reported)</t>
-  </si>
-  <si>
     <t xml:space="preserve">ALL</t>
   </si>
   <si>
-    <t xml:space="preserve">Mean of species means (chain-complete: S01, S02, S03, S04, S05, S06, S07, S09)</t>
+    <t xml:space="preserve">Mean of species means (chain-complete: S01, S02, S04, S05, S06, S07, S09)</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>
   </si>
   <si>
-    <t xml:space="preserve">Pooled over 8 chain-complete species (consumer n &gt;= 3)</t>
+    <t xml:space="preserve">Pooled over 7 chain-complete species (consumer n &gt;= 3)</t>
   </si>
   <si>
     <t xml:space="preserve">Producer price = net auction price paid to fishers (Form A buy) at the landing-linked markets M1/M6 only; Aratdar sell = auction hammer price at M1/M6; Bepari sell = Form B sell over all markets; Retailer sell = Form R vendor quote (descriptive; margins use the consumer-paid anchor); Consumer = focal-species purchases actually paid (Form C). Margins are differences of consecutive level means and telescope to the total spread. K/D-flagged prices excluded. Species without a complete chain - or with fewer than MIN_CONS consumer-paid observations - show prices but blank margins/share and are excluded from ALL (see Local_name note); Consumer_paid_n reports the actual number of consumer slips behind each share. Reporting_status lists Method 3.8 descriptive-only reasons.</t>
@@ -680,18 +680,18 @@
     <t xml:space="preserve">Payment_method_pct</t>
   </si>
   <si>
+    <t xml:space="preserve">Cash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumer (Form C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagad_app</t>
+  </si>
+  <si>
     <t xml:space="preserve">bKash</t>
   </si>
   <si>
-    <t xml:space="preserve">Consumer (Form C)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cash</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nagad_app</t>
-  </si>
-  <si>
     <t xml:space="preserve">Credit</t>
   </si>
   <si>
@@ -725,6 +725,30 @@
     <t xml:space="preserve">Total_pct</t>
   </si>
   <si>
+    <t xml:space="preserve">Day-to-day price volatility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low landings in lean season</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rising cost of ice and salt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High ice price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterlogging during monsoon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transport cost increase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delayed credit recovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rising toll and lease burden</t>
+  </si>
+  <si>
     <t xml:space="preserve">Supply syndicate control</t>
   </si>
   <si>
@@ -734,33 +758,9 @@
     <t xml:space="preserve">Competition from frozen imported fish</t>
   </si>
   <si>
-    <t xml:space="preserve">High ice price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Day-to-day price volatility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low landings in lean season</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterlogging during monsoon</t>
-  </si>
-  <si>
     <t xml:space="preserve">Irregular electricity and load-shedding</t>
   </si>
   <si>
-    <t xml:space="preserve">Rising cost of ice and salt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delayed credit recovery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rising toll and lease burden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transport cost increase</t>
-  </si>
-  <si>
     <t xml:space="preserve">% = share of that actor's respondents mentioning the problem in any of the 3 slots (multi-response).</t>
   </si>
   <si>
@@ -974,22 +974,22 @@
     <t xml:space="preserve">Purity</t>
   </si>
   <si>
+    <t xml:space="preserve">Familiar_shop</t>
+  </si>
+  <si>
     <t xml:space="preserve">Price</t>
   </si>
   <si>
     <t xml:space="preserve">Proximity</t>
   </si>
   <si>
-    <t xml:space="preserve">Familiar_shop</t>
-  </si>
-  <si>
     <t xml:space="preserve">Variety</t>
   </si>
   <si>
     <t xml:space="preserve">Mean visit interval (days)</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57</t>
+    <t xml:space="preserve">4.67</t>
   </si>
   <si>
     <t xml:space="preserve">Focal purchase source (per purchase)</t>
@@ -998,16 +998,16 @@
     <t xml:space="preserve">Mean focal-species price paid (BDT/kg)</t>
   </si>
   <si>
-    <t xml:space="preserve">699.04</t>
+    <t xml:space="preserve">752.22</t>
   </si>
   <si>
     <t xml:space="preserve">Mean purchase size (kg)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumers n=30; focal purchases n=69 (Yes today n=52).</t>
+    <t xml:space="preserve">1.76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumers n=30; focal purchases n=66 (Yes today n=54).</t>
   </si>
   <si>
     <t xml:space="preserve">Fish (local name)</t>
@@ -1019,30 +1019,30 @@
     <t xml:space="preserve">Mean_qty_kg</t>
   </si>
   <si>
+    <t xml:space="preserve">Datina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagda chingri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chatka chingri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kakra (crab)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faisya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lobster (local)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Khoira</t>
   </si>
   <si>
-    <t xml:space="preserve">Bagda chingri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Datina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kakra (crab)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chatka chingri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lobster (local)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Faisya</t>
-  </si>
-  <si>
     <t xml:space="preserve">Non-focal aquatic items consumers reported buying on the interview day (Consumer_Other_Fish sheet). Includes crustaceans (Bagda shrimp, Kakra crab) and finfish (Khoira, Datina, Moid, Faisya, lobster) - comparison items outside the ten focal marine-finfish species of Table 3.4.</t>
   </si>
   <si>
@@ -1139,445 +1139,436 @@
     <t xml:space="preserve">PAIR-M1-01</t>
   </si>
   <si>
-    <t xml:space="preserve">M1-A-03</t>
+    <t xml:space="preserve">M1-A-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1-R-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khuchra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAIR-M1-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1-A-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1-R-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAIR-M2-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2-A-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2-R-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAIR-M2-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2-A-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2-R-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAIR-M2-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2-A-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2-R-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAIR-M3-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M3-A-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M3-R-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAIR-M3-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M3-A-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M3-R-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAIR-M4-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M4-A-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M4-R-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAIR-M4-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAIR-M4-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M4-A-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M4-R-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAIR-M5-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M5-A-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M5-R-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAIR-M5-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAIR-M5-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M5-A-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M5-R-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAIR-M6-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M6-A-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M6-R-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAIR-M6-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M6-A-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M6-R-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matched-pair transaction prices (Methodology 3.3.4). Seller_sell = the seller's quoted sale price of the lot; Buyer_buy = the buyer's quoted purchase price of the same lot. Diff = seller sell - buyer buy (~0 if self-reports are consistent). Complete = both sides quoted numerically.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usable matched pairs (n)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pairs with non-zero difference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median difference (BDT/kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean difference (BDT/kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilcoxon W statistic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p-value (two-sided)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interpretation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p &gt;= 0.05: seller-sell and buyer-buy quotes of matched lots do not differ systematically - self-reported chain prices are internally consistent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilcoxon signed-rank on paired differences (seller's sell - buyer's buy) of the same matched lot (Methodology 3.3.4). Diagnostic consistency check, not a powered hypothesis test; report n alongside the result. R uses the normal approximation with tie handling when exact calculation is unavailable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wholesale_sell_mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_wholesale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retailer_sell_quote_mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_retailer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumer_paid_mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_consumer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retail_margin_quote_BDT_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retail_margin_paid_BDT_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Species x market price decomposition. Wholesale = Bepari/Faria sell quotes; Retailer quote = khuchra sell quotes; Consumer = Form C slips. The difference between quote- and paid-based margins reflects bargaining at retail. Cells with n=0 are not observed. Per Methodology 3.8 cells with n&lt;5 support descriptive statements only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test_tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Markets_qualifying</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_per_market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">df</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exploratory (n&gt;=3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1; M2; M3; M4; M5; M6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1=5; M2=4; M3=3; M4=5; M5=4; M6=3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reject H0 (p&lt;0.05): prices differ across markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2; M3; M4; M5; M6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2=3; M3=4; M4=3; M5=3; M6=4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fail to reject H0 (p&gt;=0.05)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2; M3; M4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2=4; M3=5; M4=3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1; M3; M6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1=3; M3=4; M6=5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1; M3; M4; M5; M6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1=4; M3=3; M4=5; M5=5; M6=4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1; M2; M4; M5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1=3; M2=3; M4=4; M5=5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cells &lt; n threshold in &lt;3 markets -&gt; descriptive only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kruskal-Wallis H (Methodology 3.8): do retailer selling prices of the same species differ across markets? Cells with n&gt;=5 in &gt;=3 markets use the pre-specified test; otherwise an exploratory tier (n&gt;=3) is flagged and species with thinner coverage are reported descriptively only (no pooled-across-species tests).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market_i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market_j</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">raw_p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p_holm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">significant_0.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dunn's post-hoc with Holm step-down (p_holm) following significant Kruskal-Wallis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MFS_Regular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MFS_Occasional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MFS_Never</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MFS_share_pct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chi-square (actor x MFS frequency)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chi2=2.49, df=4, p=0.6472, G-test p=0.6349, Fisher-exact p=0.6640</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cramer's V / smallest expected count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V=0.118 / min exp=4.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payment-mode adoption by trader class (Methodology 3.8 Q4). Chi-square on MFS-use frequency (Regular/Occasional/Never); because the smallest expected cell may fall below 5, the likelihood-ratio (G) test and the exact Freeman-Halton/Fisher test are reported alongside Pearson chi-square as sparse-cell fallbacks. Consumer payment method is a separate question and appears in Tables 5/8.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median_margin_BDT_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IQR_BDT_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean_margin_BDT_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bepari_Faria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mann-Whitney U: Aratdar vs Bepari_Faria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U=8, p&lt;0.0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mann-Whitney U: Aratdar vs Khuchra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U=0, p&lt;0.0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mann-Whitney U: Bepari_Faria vs Khuchra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U=35, p&lt;0.0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per-respondent mean own-quote margin = mean of (sell - buy) over species quoted with both prices on the interview day (Methodology 3.7.2: M = P_s - P_b). Mann-Whitney U per stratum pair (Q2); Holm adjustment is recommended when quoting all three comparisons.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Respondent_ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC_BDT_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net_profit_BDT_kg</t>
   </si>
   <si>
     <t xml:space="preserve">M1-R-01</t>
   </si>
   <si>
-    <t xml:space="preserve">Khuchra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAIR-M1-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1-A-04</t>
+    <t xml:space="preserve">M1-R-03</t>
   </si>
   <si>
     <t xml:space="preserve">M1-R-04</t>
   </si>
   <si>
-    <t xml:space="preserve">PAIR-M1-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1-A-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1-R-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAIR-M2-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2-A-05</t>
-  </si>
-  <si>
     <t xml:space="preserve">M2-R-02</t>
   </si>
   <si>
-    <t xml:space="preserve">PAIR-M2-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2-A-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2-R-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAIR-M3-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M3-A-03</t>
+    <t xml:space="preserve">M2-R-04</t>
   </si>
   <si>
     <t xml:space="preserve">M3-R-01</t>
   </si>
   <si>
-    <t xml:space="preserve">PAIR-M3-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAIR-M3-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M3-A-01</t>
-  </si>
-  <si>
     <t xml:space="preserve">M3-R-02</t>
   </si>
   <si>
-    <t xml:space="preserve">PAIR-M4-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M4-A-04</t>
+    <t xml:space="preserve">M3-R-05</t>
   </si>
   <si>
     <t xml:space="preserve">M4-R-03</t>
   </si>
   <si>
-    <t xml:space="preserve">PAIR-M4-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M4-A-03</t>
+    <t xml:space="preserve">M4-R-04</t>
   </si>
   <si>
     <t xml:space="preserve">M4-R-05</t>
   </si>
   <si>
-    <t xml:space="preserve">PAIR-M5-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M5-A-04</t>
+    <t xml:space="preserve">M5-R-02</t>
   </si>
   <si>
     <t xml:space="preserve">M5-R-03</t>
   </si>
   <si>
-    <t xml:space="preserve">PAIR-M5-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M5-A-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M5-R-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAIR-M5-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAIR-M6-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M6-A-04</t>
+    <t xml:space="preserve">M5-R-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M6-R-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M6-R-03</t>
   </si>
   <si>
     <t xml:space="preserve">M6-R-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAIR-M6-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M6-A-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M6-R-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAIR-M6-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M6-A-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M6-R-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matched-pair transaction prices (Methodology 3.3.4). Seller_sell = the seller's quoted sale price of the lot; Buyer_buy = the buyer's quoted purchase price of the same lot. Diff = seller sell - buyer buy (~0 if self-reports are consistent). Complete = both sides quoted numerically.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Usable matched pairs (n)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pairs with non-zero difference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median difference (BDT/kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean difference (BDT/kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wilcoxon W statistic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p-value (two-sided)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interpretation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p &gt;= 0.05: seller-sell and buyer-buy quotes of matched lots do not differ systematically - self-reported chain prices are internally consistent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wilcoxon signed-rank on paired differences (seller's sell - buyer's buy) of the same matched lot (Methodology 3.3.4). Diagnostic consistency check, not a powered hypothesis test; report n alongside the result. R uses the normal approximation with tie handling when exact calculation is unavailable.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wholesale_sell_mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n_wholesale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retailer_sell_quote_mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n_retailer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer_paid_mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n_consumer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retail_margin_quote_BDT_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retail_margin_paid_BDT_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Species x market price decomposition. Wholesale = Bepari/Faria sell quotes; Retailer quote = khuchra sell quotes; Consumer = Form C slips. The difference between quote- and paid-based margins reflects bargaining at retail. Cells with n=0 are not observed. Per Methodology 3.8 cells with n&lt;5 support descriptive statements only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test_tier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Markets_qualifying</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n_per_market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">df</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exploratory (n&gt;=3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1; M2; M3; M4; M5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1=4; M2=4; M3=5; M4=4; M5=4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reject H0 (p&lt;0.05): prices differ across markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1; M2; M3; M4; M5; M6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1=5; M2=3; M3=4; M4=3; M5=3; M6=4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M3; M5; M6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M3=3; M5=4; M6=5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2; M3; M5; M6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2=4; M3=3; M5=3; M6=4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fail to reject H0 (p&gt;=0.05)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2; M3; M4; M5; M6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2=3; M3=4; M4=4; M5=3; M6=5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1; M3; M4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1=4; M3=4; M4=4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not run</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cells &lt; n threshold in &lt;3 markets -&gt; descriptive only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kruskal-Wallis H (Methodology 3.8): do retailer selling prices of the same species differ across markets? Cells with n&gt;=5 in &gt;=3 markets use the pre-specified test; otherwise an exploratory tier (n&gt;=3) is flagged and species with thinner coverage are reported descriptively only (no pooled-across-species tests).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Market_i</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Market_j</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">raw_p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p_holm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">significant_0.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dunn's post-hoc with Holm step-down (p_holm) following significant Kruskal-Wallis.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MFS_Regular</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MFS_Occasional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MFS_Never</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MFS_share_pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chi-square (actor x MFS frequency)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chi2=1.22, df=4, p=0.8749, G-test p=0.8809, Fisher-exact p=0.8945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cramer's V / smallest expected count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V=0.082 / min exp=3.67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payment-mode adoption by trader class (Methodology 3.8 Q4). Chi-square on MFS-use frequency (Regular/Occasional/Never); because the smallest expected cell may fall below 5, the likelihood-ratio (G) test and the exact Freeman-Halton/Fisher test are reported alongside Pearson chi-square as sparse-cell fallbacks. Consumer payment method is a separate question and appears in Tables 5/8.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median_margin_BDT_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IQR_BDT_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean_margin_BDT_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bepari_Faria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mann-Whitney U: Aratdar vs Bepari_Faria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30/30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U=0, p&lt;0.0001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mann-Whitney U: Aratdar vs Khuchra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mann-Whitney U: Bepari_Faria vs Khuchra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U=10, p&lt;0.0001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per-respondent mean own-quote margin = mean of (sell - buy) over species quoted with both prices on the interview day (Methodology 3.7.2: M = P_s - P_b). Mann-Whitney U per stratum pair (Q2); Holm adjustment is recommended when quoting all three comparisons.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Respondent_ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MC_BDT_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net_profit_BDT_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1-R-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1-R-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2-R-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2-R-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2-R-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M3-R-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M3-R-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M3-R-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M4-R-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M4-R-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M4-R-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M5-R-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M5-R-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M5-R-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M6-R-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M6-R-02</t>
   </si>
   <si>
     <t xml:space="preserve">Spearman rho(MC, net margin)</t>
@@ -2133,7 +2124,7 @@
         <v>21</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E14" t="n">
         <v>4</v>
@@ -2189,7 +2180,7 @@
         <v>29</v>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
         <v>11</v>
@@ -2245,7 +2236,7 @@
         <v>37</v>
       </c>
       <c r="D22" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E22" t="n">
         <v>7</v>
@@ -2359,10 +2350,10 @@
         <v>308</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>53.3</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="7">
@@ -2373,10 +2364,10 @@
         <v>309</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>46.7</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="8">
@@ -2387,10 +2378,10 @@
         <v>215</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>36.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -2401,10 +2392,10 @@
         <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>36.7</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="10">
@@ -2443,10 +2434,10 @@
         <v>312</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>33.3</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="13">
@@ -2457,10 +2448,10 @@
         <v>313</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>23.3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -2471,10 +2462,10 @@
         <v>314</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>23.3</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="15">
@@ -2496,78 +2487,92 @@
         <v>311</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>316</v>
+        <v>87</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>3.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C17" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D17" t="n">
-        <v>30</v>
-      </c>
-      <c r="E17"/>
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.3</v>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>61</v>
+        <v>318</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>71</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="E18" s="6"/>
     </row>
     <row r="19">
       <c r="B19" t="s">
         <v>319</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="E19" t="n">
-        <v>4.3</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>321</v>
+        <v>105</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="E20" s="6"/>
+        <v>3</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="21">
       <c r="B21" t="s">
+        <v>320</v>
+      </c>
+      <c r="C21" t="s">
+        <v>321</v>
+      </c>
+      <c r="D21" t="n">
+        <v>54</v>
+      </c>
+      <c r="E21"/>
+    </row>
+    <row r="22">
+      <c r="B22" t="s">
         <v>322</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C22" t="s">
         <v>323</v>
       </c>
-      <c r="D21" t="n">
-        <v>52</v>
-      </c>
-      <c r="E21"/>
+      <c r="D22" t="n">
+        <v>54</v>
+      </c>
+      <c r="E22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2618,13 +2623,13 @@
         <v>328</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>268</v>
+        <v>378.33</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="7">
@@ -2635,7 +2640,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>1033.33</v>
+        <v>995</v>
       </c>
       <c r="E7" t="n">
         <v>0.83</v>
@@ -2646,13 +2651,13 @@
         <v>330</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>356.67</v>
+        <v>467.5</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>0.67</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="9">
@@ -2660,13 +2665,13 @@
         <v>331</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>216.67</v>
+        <v>575</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="10">
@@ -2677,10 +2682,10 @@
         <v>2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>570</v>
+        <v>180</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11">
@@ -2688,13 +2693,13 @@
         <v>333</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>440</v>
+        <v>332.5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="12">
@@ -2702,13 +2707,13 @@
         <v>334</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>2615</v>
+        <v>2800</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>0.5</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="13">
@@ -2719,10 +2724,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>310</v>
+        <v>345</v>
       </c>
       <c r="E13" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -2774,13 +2779,13 @@
         <v>341</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>27.84</v>
+        <v>27.01</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="7">
@@ -2788,13 +2793,13 @@
         <v>342</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>99.58</v>
+        <v>108.26</v>
       </c>
       <c r="E7" t="n">
-        <v>11.7</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="8">
@@ -2802,13 +2807,13 @@
         <v>343</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>118.97</v>
+        <v>124.18</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>14</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="9">
@@ -2816,13 +2821,13 @@
         <v>344</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>246.39</v>
+        <v>259.45</v>
       </c>
       <c r="E9" t="n">
-        <v>29.1</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="10">
@@ -2830,11 +2835,11 @@
         <v>345</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D10"/>
       <c r="E10" t="n">
-        <v>70.9</v>
+        <v>69.6</v>
       </c>
     </row>
   </sheetData>
@@ -2898,22 +2903,22 @@
         <v>348</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>1416</v>
+        <v>1441</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1480</v>
+        <v>1558</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1491</v>
+        <v>1551</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>1497</v>
+        <v>1536</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1571</v>
+        <v>1654</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>1445</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="7">
@@ -2921,62 +2926,66 @@
         <v>349</v>
       </c>
       <c r="C7" t="n">
-        <v>1586</v>
+        <v>1708</v>
       </c>
       <c r="D7" t="n">
-        <v>1603</v>
+        <v>1689</v>
       </c>
       <c r="E7" t="n">
-        <v>1645</v>
+        <v>1713</v>
       </c>
       <c r="F7" t="n">
-        <v>1597</v>
+        <v>1615</v>
       </c>
       <c r="G7" t="n">
-        <v>1717</v>
+        <v>1742</v>
       </c>
       <c r="H7" t="n">
-        <v>1590</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="C8" s="6"/>
+      <c r="C8" s="6" t="n">
+        <v>998</v>
+      </c>
       <c r="D8" s="6" t="n">
-        <v>1080</v>
+        <v>1088</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>1047</v>
-      </c>
-      <c r="F8" s="6"/>
+        <v>1130</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>1126</v>
+      </c>
       <c r="G8" s="6" t="n">
-        <v>1112</v>
+        <v>1090</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>1045</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="s">
         <v>351</v>
       </c>
-      <c r="C9"/>
-      <c r="D9" t="n">
-        <v>958</v>
-      </c>
+      <c r="C9" t="n">
+        <v>886</v>
+      </c>
+      <c r="D9"/>
       <c r="E9" t="n">
-        <v>938</v>
+        <v>994</v>
       </c>
       <c r="F9" t="n">
-        <v>895</v>
+        <v>980</v>
       </c>
       <c r="G9" t="n">
-        <v>963</v>
+        <v>955</v>
       </c>
       <c r="H9" t="n">
-        <v>902</v>
+        <v>907</v>
       </c>
     </row>
     <row r="10">
@@ -2984,22 +2993,22 @@
         <v>352</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>585</v>
+        <v>600</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>614</v>
+        <v>629</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>569</v>
+        <v>612</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>612</v>
+        <v>622</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>551</v>
+        <v>582</v>
       </c>
     </row>
     <row r="11">
@@ -3007,22 +3016,22 @@
         <v>353</v>
       </c>
       <c r="C11" t="n">
-        <v>416</v>
+        <v>463</v>
       </c>
       <c r="D11" t="n">
-        <v>472</v>
+        <v>498</v>
       </c>
       <c r="E11" t="n">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="F11" t="n">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="G11" t="n">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="H11" t="n">
-        <v>460</v>
+        <v>486</v>
       </c>
     </row>
     <row r="12">
@@ -3030,49 +3039,45 @@
         <v>354</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>555</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>595</v>
-      </c>
+        <v>567</v>
+      </c>
+      <c r="E12" s="6"/>
       <c r="F12" s="6" t="n">
-        <v>563</v>
-      </c>
-      <c r="G12" s="6"/>
+        <v>575</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>545</v>
+      </c>
       <c r="H12" s="6" t="n">
-        <v>505</v>
+        <v>520</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="s">
         <v>355</v>
       </c>
-      <c r="C13" t="n">
-        <v>310</v>
-      </c>
+      <c r="C13"/>
       <c r="D13"/>
       <c r="E13"/>
       <c r="F13"/>
-      <c r="G13"/>
-      <c r="H13" t="n">
-        <v>340</v>
-      </c>
+      <c r="G13" t="n">
+        <v>345</v>
+      </c>
+      <c r="H13"/>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
         <v>356</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
-      <c r="F14" s="6" t="n">
-        <v>279</v>
-      </c>
+      <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
     </row>
@@ -3081,11 +3086,13 @@
         <v>357</v>
       </c>
       <c r="C15"/>
-      <c r="D15"/>
-      <c r="E15"/>
-      <c r="F15" t="n">
-        <v>230</v>
-      </c>
+      <c r="D15" t="n">
+        <v>255</v>
+      </c>
+      <c r="E15" t="n">
+        <v>250</v>
+      </c>
+      <c r="F15"/>
       <c r="G15"/>
       <c r="H15"/>
     </row>
@@ -3110,7 +3117,7 @@
     </row>
     <row r="3">
       <c r="B3" s="4" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="4">
@@ -3134,7 +3141,7 @@
         <v>243</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
         <v>360</v>
@@ -3169,7 +3176,7 @@
         <v>260</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>368</v>
@@ -3178,7 +3185,7 @@
         <v>58</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1024.92</v>
+        <v>783.76</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>369</v>
@@ -3187,10 +3194,10 @@
         <v>370</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>1030</v>
+        <v>783.76</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>-5.08</v>
+        <v>0</v>
       </c>
       <c r="L6" s="6" t="b">
         <v>1</v>
@@ -3204,7 +3211,7 @@
         <v>260</v>
       </c>
       <c r="D7" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E7" t="s">
         <v>372</v>
@@ -3213,7 +3220,7 @@
         <v>58</v>
       </c>
       <c r="G7" t="n">
-        <v>1145.5</v>
+        <v>348.34</v>
       </c>
       <c r="H7" t="s">
         <v>373</v>
@@ -3222,10 +3229,10 @@
         <v>370</v>
       </c>
       <c r="J7" t="n">
-        <v>1145</v>
+        <v>350</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5</v>
+        <v>-1.66</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
@@ -3236,10 +3243,10 @@
         <v>374</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>375</v>
@@ -3248,7 +3255,7 @@
         <v>58</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>1004.82</v>
+        <v>870.85</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>376</v>
@@ -3257,10 +3264,10 @@
         <v>370</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>1005</v>
+        <v>870.85</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="L8" s="6" t="b">
         <v>1</v>
@@ -3274,7 +3281,7 @@
         <v>273</v>
       </c>
       <c r="D9" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="E9" t="s">
         <v>378</v>
@@ -3283,7 +3290,7 @@
         <v>58</v>
       </c>
       <c r="G9" t="n">
-        <v>435.42</v>
+        <v>1205.79</v>
       </c>
       <c r="H9" t="s">
         <v>379</v>
@@ -3292,10 +3299,10 @@
         <v>370</v>
       </c>
       <c r="J9" t="n">
-        <v>435</v>
+        <v>1205.79</v>
       </c>
       <c r="K9" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
@@ -3309,7 +3316,7 @@
         <v>273</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>381</v>
@@ -3318,7 +3325,7 @@
         <v>58</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>1292.87</v>
+        <v>448.82</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>382</v>
@@ -3327,10 +3334,10 @@
         <v>370</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>1290</v>
+        <v>450</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>2.87</v>
+        <v>-1.18</v>
       </c>
       <c r="L10" s="6" t="b">
         <v>1</v>
@@ -3344,7 +3351,7 @@
         <v>283</v>
       </c>
       <c r="D11" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="E11" t="s">
         <v>384</v>
@@ -3353,7 +3360,7 @@
         <v>58</v>
       </c>
       <c r="G11" t="n">
-        <v>1091.91</v>
+        <v>756.97</v>
       </c>
       <c r="H11" t="s">
         <v>385</v>
@@ -3362,10 +3369,10 @@
         <v>370</v>
       </c>
       <c r="J11" t="n">
-        <v>1095</v>
+        <v>760</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.09</v>
+        <v>-3.03</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
@@ -3379,49 +3386,63 @@
         <v>283</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
+        <v>130</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1299.57</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1300</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>-0.43</v>
+      </c>
       <c r="L12" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C13" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="D13" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="E13" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F13" t="s">
         <v>58</v>
       </c>
       <c r="G13" t="n">
-        <v>468.92</v>
+        <v>1212.49</v>
       </c>
       <c r="H13" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I13" t="s">
         <v>370</v>
       </c>
       <c r="J13" t="n">
-        <v>465</v>
+        <v>1219.19</v>
       </c>
       <c r="K13" t="n">
-        <v>3.92</v>
+        <v>-6.7</v>
       </c>
       <c r="L13" t="b">
         <v>1</v>
@@ -3429,37 +3450,23 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>289</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>391</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>1205.79</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>1205</v>
-      </c>
-      <c r="K14" s="6" t="n">
-        <v>0.79</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
       <c r="L14" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -3470,7 +3477,7 @@
         <v>289</v>
       </c>
       <c r="D15" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E15" t="s">
         <v>394</v>
@@ -3479,7 +3486,7 @@
         <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>401.93</v>
+        <v>1205.79</v>
       </c>
       <c r="H15" t="s">
         <v>395</v>
@@ -3488,10 +3495,10 @@
         <v>370</v>
       </c>
       <c r="J15" t="n">
-        <v>401.93</v>
+        <v>1205</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="L15" t="b">
         <v>1</v>
@@ -3505,7 +3512,7 @@
         <v>294</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>397</v>
@@ -3514,7 +3521,7 @@
         <v>58</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>468.92</v>
+        <v>361.74</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>398</v>
@@ -3523,10 +3530,10 @@
         <v>370</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>465</v>
+        <v>360</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>3.92</v>
+        <v>1.74</v>
       </c>
       <c r="L16" s="6" t="b">
         <v>1</v>
@@ -3540,52 +3547,52 @@
         <v>294</v>
       </c>
       <c r="D17" t="s">
-        <v>127</v>
-      </c>
-      <c r="E17" t="s">
-        <v>400</v>
-      </c>
-      <c r="F17" t="s">
-        <v>58</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1138.8</v>
-      </c>
-      <c r="H17" t="s">
-        <v>401</v>
-      </c>
-      <c r="I17" t="s">
-        <v>370</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1135</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.8</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17"/>
+      <c r="K17"/>
       <c r="L17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>294</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
+        <v>140</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>468.92</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>465</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>3.92</v>
+      </c>
       <c r="L18" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -3596,7 +3603,7 @@
         <v>300</v>
       </c>
       <c r="D19" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E19" t="s">
         <v>404</v>
@@ -3605,7 +3612,7 @@
         <v>58</v>
       </c>
       <c r="G19" t="n">
-        <v>1185.69</v>
+        <v>797.16</v>
       </c>
       <c r="H19" t="s">
         <v>405</v>
@@ -3614,82 +3621,47 @@
         <v>370</v>
       </c>
       <c r="J19" t="n">
-        <v>1185</v>
+        <v>795</v>
       </c>
       <c r="K19" t="n">
-        <v>0.69</v>
+        <v>2.16</v>
       </c>
       <c r="L19" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="6" t="s">
+      <c r="B20" t="s">
         <v>406</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" t="s">
         <v>300</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="E20" s="6" t="s">
+      <c r="D20" t="s">
+        <v>137</v>
+      </c>
+      <c r="E20" t="s">
         <v>407</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" t="s">
         <v>58</v>
       </c>
-      <c r="G20" s="6" t="n">
-        <v>415.33</v>
-      </c>
-      <c r="H20" s="6" t="s">
+      <c r="G20" t="n">
+        <v>730.17</v>
+      </c>
+      <c r="H20" t="s">
         <v>408</v>
       </c>
-      <c r="I20" s="6" t="s">
+      <c r="I20" t="s">
         <v>370</v>
       </c>
-      <c r="J20" s="6" t="n">
-        <v>415</v>
-      </c>
-      <c r="K20" s="6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="L20" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="s">
-        <v>409</v>
-      </c>
-      <c r="C21" t="s">
-        <v>300</v>
-      </c>
-      <c r="D21" t="s">
-        <v>140</v>
-      </c>
-      <c r="E21" t="s">
-        <v>410</v>
-      </c>
-      <c r="F21" t="s">
-        <v>58</v>
-      </c>
-      <c r="G21" t="n">
-        <v>422.03</v>
-      </c>
-      <c r="H21" t="s">
-        <v>411</v>
-      </c>
-      <c r="I21" t="s">
-        <v>370</v>
-      </c>
-      <c r="J21" t="n">
-        <v>420</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="L21" t="b">
+      <c r="J20" t="n">
+        <v>730</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="L20" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3714,7 +3686,7 @@
     </row>
     <row r="3">
       <c r="B3" s="4" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="4">
@@ -3731,58 +3703,58 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C7" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C9" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C11" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C12" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
   </sheetData>
@@ -3806,7 +3778,7 @@
     </row>
     <row r="3">
       <c r="B3" s="4" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="4">
@@ -3829,165 +3801,173 @@
         <v>243</v>
       </c>
       <c r="D5" t="s">
+        <v>425</v>
+      </c>
+      <c r="E5" t="s">
+        <v>426</v>
+      </c>
+      <c r="F5" t="s">
+        <v>427</v>
+      </c>
+      <c r="G5" t="s">
         <v>428</v>
       </c>
-      <c r="E5" t="s">
+      <c r="H5" t="s">
         <v>429</v>
       </c>
-      <c r="F5" t="s">
+      <c r="I5" t="s">
         <v>430</v>
       </c>
-      <c r="G5" t="s">
+      <c r="J5" t="s">
         <v>431</v>
       </c>
-      <c r="H5" t="s">
+      <c r="K5" t="s">
         <v>432</v>
-      </c>
-      <c r="I5" t="s">
-        <v>433</v>
-      </c>
-      <c r="J5" t="s">
-        <v>434</v>
-      </c>
-      <c r="K5" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>260</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1138.8</v>
+        <v>1155.55</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>1416.25</v>
+        <v>1441.05</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>1352.5</v>
+        <v>1410</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>277.45</v>
+        <v>285.5</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>213.7</v>
+        <v>254.45</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C7" t="s">
         <v>273</v>
       </c>
       <c r="D7" t="n">
-        <v>1266.08</v>
+        <v>1329.72</v>
       </c>
       <c r="E7" t="n">
         <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>1480</v>
+        <v>1557.74</v>
       </c>
       <c r="G7" t="n">
         <v>4</v>
       </c>
-      <c r="H7"/>
+      <c r="H7" t="n">
+        <v>1520</v>
+      </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>213.92</v>
-      </c>
-      <c r="K7"/>
+        <v>228.02</v>
+      </c>
+      <c r="K7" t="n">
+        <v>190.28</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>283</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1333.07</v>
+        <v>1311.63</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1491</v>
+        <v>1550.68</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>1456.67</v>
+        <v>1582.5</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>157.93</v>
+        <v>239.05</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>123.6</v>
+        <v>270.87</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C9" t="s">
         <v>289</v>
       </c>
       <c r="D9" t="n">
-        <v>1225.88</v>
+        <v>1286.17</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>1496.76</v>
+        <v>1535.79</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H9"/>
+        <v>5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1552.5</v>
+      </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>270.88</v>
-      </c>
-      <c r="K9"/>
+        <v>249.62</v>
+      </c>
+      <c r="K9" t="n">
+        <v>266.33</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>294</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1282.82</v>
+        <v>1303.59</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>1570.75</v>
+        <v>1653.75</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>4</v>
@@ -3997,89 +3977,89 @@
         <v>0</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>287.93</v>
+        <v>350.16</v>
       </c>
       <c r="K10" s="6"/>
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C11" t="s">
         <v>300</v>
       </c>
       <c r="D11" t="n">
-        <v>1244.31</v>
+        <v>1260.72</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>1445</v>
+        <v>1475.65</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>1445</v>
+        <v>1420</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>200.69</v>
+        <v>214.93</v>
       </c>
       <c r="K11" t="n">
-        <v>200.69</v>
+        <v>159.28</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>260</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>1309.62</v>
+        <v>1343.12</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>1586</v>
+        <v>1707.5</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>1475</v>
+        <v>1585</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>276.38</v>
+        <v>364.38</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>165.38</v>
+        <v>241.88</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C13" t="s">
         <v>273</v>
       </c>
       <c r="D13" t="n">
-        <v>1415.13</v>
+        <v>1426.85</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>1603.33</v>
+        <v>1688.58</v>
       </c>
       <c r="G13" t="n">
         <v>3</v>
@@ -4089,53 +4069,57 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>188.2</v>
+        <v>261.73</v>
       </c>
       <c r="K13"/>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>283</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1426.85</v>
+        <v>1375.49</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>1645</v>
+        <v>1713.3</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="H14" s="6"/>
+      <c r="H14" s="6" t="n">
+        <v>1755</v>
+      </c>
       <c r="I14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>218.15</v>
-      </c>
-      <c r="K14" s="6"/>
+        <v>337.81</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>379.51</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C15" t="s">
         <v>289</v>
       </c>
       <c r="D15" t="n">
-        <v>1343.11</v>
+        <v>1444.27</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F15" t="n">
-        <v>1596.67</v>
+        <v>1615</v>
       </c>
       <c r="G15" t="n">
         <v>3</v>
@@ -4145,57 +4129,53 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>253.56</v>
+        <v>170.73</v>
       </c>
       <c r="K15"/>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>294</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>1429.53</v>
+        <v>1498.86</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>1717.17</v>
+        <v>1741.67</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="H16" s="6" t="n">
-        <v>1685</v>
-      </c>
+      <c r="H16" s="6"/>
       <c r="I16" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>287.64</v>
-      </c>
-      <c r="K16" s="6" t="n">
-        <v>255.47</v>
-      </c>
+        <v>242.81</v>
+      </c>
+      <c r="K16" s="6"/>
     </row>
     <row r="17">
       <c r="B17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C17" t="s">
         <v>300</v>
       </c>
       <c r="D17" t="n">
-        <v>1321.34</v>
+        <v>1359.86</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>1590</v>
+        <v>1564.36</v>
       </c>
       <c r="G17" t="n">
         <v>4</v>
@@ -4205,181 +4185,181 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>268.66</v>
+        <v>204.5</v>
       </c>
       <c r="K17"/>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>260</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>817.26</v>
+        <v>904.34</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="6"/>
+      <c r="F18" s="6" t="n">
+        <v>998.12</v>
+      </c>
       <c r="G18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="6"/>
+        <v>1</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1015</v>
+      </c>
       <c r="I18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
+        <v>1</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>93.78</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>110.66</v>
+      </c>
     </row>
     <row r="19">
       <c r="B19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C19" t="s">
         <v>273</v>
       </c>
       <c r="D19" t="n">
-        <v>886.48</v>
+        <v>954.58</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>1080</v>
+        <v>1088.06</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1055</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H19"/>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>193.52</v>
-      </c>
-      <c r="K19" t="n">
-        <v>168.52</v>
-      </c>
+        <v>133.48</v>
+      </c>
+      <c r="K19"/>
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>283</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>895.41</v>
+        <v>926.11</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>1046.67</v>
+        <v>1129.82</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H20" s="6"/>
       <c r="I20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>151.26</v>
+        <v>203.71</v>
       </c>
       <c r="K20" s="6"/>
     </row>
     <row r="21">
       <c r="B21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C21" t="s">
         <v>289</v>
       </c>
       <c r="D21" t="n">
-        <v>877.54</v>
+        <v>931.13</v>
       </c>
       <c r="E21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1125.6</v>
+      </c>
+      <c r="G21" t="n">
         <v>3</v>
-      </c>
-      <c r="F21"/>
-      <c r="G21" t="n">
-        <v>0</v>
       </c>
       <c r="H21"/>
       <c r="I21" t="n">
         <v>0</v>
       </c>
-      <c r="J21"/>
+      <c r="J21" t="n">
+        <v>194.47</v>
+      </c>
       <c r="K21"/>
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>294</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>919.41</v>
+        <v>993.1</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1112.5</v>
+        <v>1090</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>1075</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H22" s="6"/>
       <c r="I22" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>193.09</v>
-      </c>
-      <c r="K22" s="6" t="n">
-        <v>155.59</v>
-      </c>
+        <v>96.9</v>
+      </c>
+      <c r="K22" s="6"/>
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C23" t="s">
         <v>300</v>
       </c>
       <c r="D23" t="n">
-        <v>866.38</v>
+        <v>855.22</v>
       </c>
       <c r="E23" t="n">
         <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>1045</v>
+        <v>1087.5</v>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
-      </c>
-      <c r="H23" t="n">
-        <v>970</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H23"/>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>178.62</v>
-      </c>
-      <c r="K23" t="n">
-        <v>103.62</v>
-      </c>
+        <v>232.28</v>
+      </c>
+      <c r="K23"/>
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
@@ -4389,21 +4369,29 @@
         <v>260</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>710.08</v>
+        <v>730.17</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F24" s="6"/>
+      <c r="F24" s="6" t="n">
+        <v>885.85</v>
+      </c>
       <c r="G24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="6"/>
+        <v>3</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>905</v>
+      </c>
       <c r="I24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>155.68</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>174.83</v>
+      </c>
     </row>
     <row r="25">
       <c r="B25" t="s">
@@ -4413,25 +4401,25 @@
         <v>273</v>
       </c>
       <c r="D25" t="n">
-        <v>803.86</v>
+        <v>793.81</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F25" t="n">
-        <v>957.5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F25"/>
       <c r="G25" t="n">
-        <v>4</v>
-      </c>
-      <c r="H25"/>
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>925</v>
+      </c>
       <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>153.64</v>
-      </c>
-      <c r="K25"/>
+        <v>1</v>
+      </c>
+      <c r="J25"/>
+      <c r="K25" t="n">
+        <v>131.19</v>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="s">
@@ -4441,29 +4429,25 @@
         <v>283</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>788.23</v>
+        <v>826.19</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>938.33</v>
+        <v>993.73</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>925</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H26" s="6"/>
       <c r="I26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>150.1</v>
-      </c>
-      <c r="K26" s="6" t="n">
-        <v>136.77</v>
-      </c>
+        <v>167.54</v>
+      </c>
+      <c r="K26" s="6"/>
     </row>
     <row r="27">
       <c r="B27" t="s">
@@ -4473,29 +4457,25 @@
         <v>289</v>
       </c>
       <c r="D27" t="n">
-        <v>743.57</v>
+        <v>790.46</v>
       </c>
       <c r="E27" t="n">
         <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>895</v>
+        <v>980</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
-      </c>
-      <c r="H27" t="n">
-        <v>860</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H27"/>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>151.43</v>
-      </c>
-      <c r="K27" t="n">
-        <v>116.43</v>
-      </c>
+        <v>189.54</v>
+      </c>
+      <c r="K27"/>
     </row>
     <row r="28">
       <c r="B28" s="6" t="s">
@@ -4505,23 +4485,23 @@
         <v>294</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>790.46</v>
+        <v>857.45</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>963.33</v>
+        <v>955</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="6"/>
       <c r="I28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>172.87</v>
+        <v>97.55</v>
       </c>
       <c r="K28" s="6"/>
     </row>
@@ -4533,29 +4513,25 @@
         <v>300</v>
       </c>
       <c r="D29" t="n">
-        <v>741.89</v>
+        <v>770.37</v>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>902.5</v>
+        <v>906.57</v>
       </c>
       <c r="G29" t="n">
-        <v>4</v>
-      </c>
-      <c r="H29" t="n">
-        <v>877.5</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="H29"/>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>160.61</v>
-      </c>
-      <c r="K29" t="n">
-        <v>135.61</v>
-      </c>
+        <v>136.2</v>
+      </c>
+      <c r="K29"/>
     </row>
     <row r="30">
       <c r="B30" s="6" t="s">
@@ -4565,28 +4541,28 @@
         <v>260</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>485</v>
+        <v>483.66</v>
       </c>
       <c r="E30" s="6" t="n">
         <v>5</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>565</v>
+        <v>561.08</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>545</v>
+        <v>572.5</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>80</v>
+        <v>77.42</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>60</v>
+        <v>88.84</v>
       </c>
     </row>
     <row r="31">
@@ -4597,28 +4573,28 @@
         <v>273</v>
       </c>
       <c r="D31" t="n">
-        <v>495.71</v>
+        <v>518.04</v>
       </c>
       <c r="E31" t="n">
         <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>585</v>
+        <v>599.55</v>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>615</v>
+        <v>587.5</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
-        <v>89.29</v>
+        <v>81.51</v>
       </c>
       <c r="K31" t="n">
-        <v>119.29</v>
+        <v>69.46</v>
       </c>
     </row>
     <row r="32">
@@ -4629,28 +4605,28 @@
         <v>283</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>527.53</v>
+        <v>515.81</v>
       </c>
       <c r="E32" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>613.75</v>
+        <v>629.33</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>590</v>
+        <v>627.5</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>86.22</v>
+        <v>113.52</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>62.47</v>
+        <v>111.69</v>
       </c>
     </row>
     <row r="33">
@@ -4661,28 +4637,28 @@
         <v>289</v>
       </c>
       <c r="D33" t="n">
-        <v>524.74</v>
+        <v>515.81</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F33" t="n">
-        <v>569.05</v>
+        <v>612.28</v>
       </c>
       <c r="G33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H33" t="n">
-        <v>585</v>
+        <v>615</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>44.31</v>
+        <v>96.47</v>
       </c>
       <c r="K33" t="n">
-        <v>60.26</v>
+        <v>99.19</v>
       </c>
     </row>
     <row r="34">
@@ -4693,28 +4669,28 @@
         <v>294</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>518.04</v>
+        <v>515.81</v>
       </c>
       <c r="E34" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>611.53</v>
+        <v>622</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>610</v>
+        <v>647.5</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>93.49</v>
+        <v>106.19</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>91.96</v>
+        <v>131.69</v>
       </c>
     </row>
     <row r="35">
@@ -4725,29 +4701,25 @@
         <v>300</v>
       </c>
       <c r="D35" t="n">
-        <v>462.22</v>
+        <v>497.05</v>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F35" t="n">
-        <v>551</v>
+        <v>581.92</v>
       </c>
       <c r="G35" t="n">
-        <v>5</v>
-      </c>
-      <c r="H35" t="n">
-        <v>580</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H35"/>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>88.78</v>
-      </c>
-      <c r="K35" t="n">
-        <v>117.78</v>
-      </c>
+        <v>84.87</v>
+      </c>
+      <c r="K35"/>
     </row>
     <row r="36">
       <c r="B36" s="6" t="s">
@@ -4757,29 +4729,25 @@
         <v>260</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>360.06</v>
+        <v>377.37</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>416.25</v>
+        <v>463.33</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="H36" s="6" t="n">
-        <v>420</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H36" s="6"/>
       <c r="I36" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>56.19</v>
-      </c>
-      <c r="K36" s="6" t="n">
-        <v>59.94</v>
-      </c>
+        <v>85.96</v>
+      </c>
+      <c r="K36" s="6"/>
     </row>
     <row r="37">
       <c r="B37" t="s">
@@ -4789,28 +4757,28 @@
         <v>273</v>
       </c>
       <c r="D37" t="n">
-        <v>378.49</v>
+        <v>405.28</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F37" t="n">
-        <v>472.5</v>
+        <v>497.94</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>443.33</v>
+        <v>450</v>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>94.01</v>
+        <v>92.66</v>
       </c>
       <c r="K37" t="n">
-        <v>64.84</v>
+        <v>44.72</v>
       </c>
     </row>
     <row r="38">
@@ -4821,28 +4789,28 @@
         <v>283</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>385.85</v>
+        <v>415.33</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>457.5</v>
+        <v>461.67</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>84.15</v>
+        <v>79.67</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>71.65</v>
+        <v>46.34</v>
       </c>
     </row>
     <row r="39">
@@ -4853,28 +4821,28 @@
         <v>289</v>
       </c>
       <c r="D39" t="n">
-        <v>390.77</v>
+        <v>404.16</v>
       </c>
       <c r="E39" t="n">
         <v>3</v>
       </c>
       <c r="F39" t="n">
-        <v>463.06</v>
+        <v>461.25</v>
       </c>
       <c r="G39" t="n">
         <v>4</v>
       </c>
       <c r="H39" t="n">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="I39" t="n">
         <v>2</v>
       </c>
       <c r="J39" t="n">
-        <v>72.29</v>
+        <v>57.09</v>
       </c>
       <c r="K39" t="n">
-        <v>54.23</v>
+        <v>55.84</v>
       </c>
     </row>
     <row r="40">
@@ -4885,28 +4853,28 @@
         <v>294</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>393</v>
+        <v>423.7</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>484.46</v>
+        <v>500</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>468.33</v>
+        <v>480</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>91.46</v>
+        <v>76.3</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>75.33</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="41">
@@ -4917,28 +4885,28 @@
         <v>300</v>
       </c>
       <c r="D41" t="n">
-        <v>375.13</v>
+        <v>379.15</v>
       </c>
       <c r="E41" t="n">
+        <v>5</v>
+      </c>
+      <c r="F41" t="n">
+        <v>486.16</v>
+      </c>
+      <c r="G41" t="n">
         <v>2</v>
       </c>
-      <c r="F41" t="n">
-        <v>460</v>
-      </c>
-      <c r="G41" t="n">
-        <v>1</v>
-      </c>
       <c r="H41" t="n">
-        <v>425</v>
+        <v>457.5</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
-        <v>84.87</v>
+        <v>107.01</v>
       </c>
       <c r="K41" t="n">
-        <v>49.87</v>
+        <v>78.35</v>
       </c>
     </row>
     <row r="42">
@@ -4949,28 +4917,28 @@
         <v>260</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>433.19</v>
+        <v>428.72</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>527.5</v>
+        <v>520.63</v>
       </c>
       <c r="G42" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>502.5</v>
+      </c>
+      <c r="I42" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H42" s="6" t="n">
-        <v>510</v>
-      </c>
-      <c r="I42" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="J42" s="6" t="n">
-        <v>94.31</v>
+        <v>91.91</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>76.81</v>
+        <v>73.78</v>
       </c>
     </row>
     <row r="43">
@@ -4981,16 +4949,16 @@
         <v>273</v>
       </c>
       <c r="D43" t="n">
-        <v>462.22</v>
+        <v>457.75</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F43" t="n">
-        <v>555</v>
+        <v>567.33</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H43" t="n">
         <v>535</v>
@@ -4999,10 +4967,10 @@
         <v>1</v>
       </c>
       <c r="J43" t="n">
-        <v>92.78</v>
+        <v>109.58</v>
       </c>
       <c r="K43" t="n">
-        <v>72.78</v>
+        <v>77.25</v>
       </c>
     </row>
     <row r="44">
@@ -5018,24 +4986,16 @@
       <c r="E44" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F44" s="6" t="n">
-        <v>595</v>
-      </c>
+      <c r="F44" s="6"/>
       <c r="G44" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="6" t="n">
-        <v>550</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H44" s="6"/>
       <c r="I44" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="6" t="n">
-        <v>146.18</v>
-      </c>
-      <c r="K44" s="6" t="n">
-        <v>101.18</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
     </row>
     <row r="45">
       <c r="B45" t="s">
@@ -5045,28 +5005,28 @@
         <v>289</v>
       </c>
       <c r="D45" t="n">
-        <v>455.52</v>
+        <v>442.12</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" t="n">
-        <v>562.7</v>
+        <v>575</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>530</v>
+        <v>545</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>107.18</v>
+        <v>132.88</v>
       </c>
       <c r="K45" t="n">
-        <v>74.48</v>
+        <v>102.88</v>
       </c>
     </row>
     <row r="46">
@@ -5077,24 +5037,28 @@
         <v>294</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>455.52</v>
+        <v>499.06</v>
       </c>
       <c r="E46" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F46" s="6"/>
+      <c r="F46" s="6" t="n">
+        <v>545</v>
+      </c>
       <c r="G46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>547.5</v>
+        <v>566.67</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J46" s="6"/>
+        <v>3</v>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v>45.94</v>
+      </c>
       <c r="K46" s="6" t="n">
-        <v>91.98</v>
+        <v>67.61</v>
       </c>
     </row>
     <row r="47">
@@ -5104,30 +5068,22 @@
       <c r="C47" t="s">
         <v>300</v>
       </c>
-      <c r="D47" t="n">
-        <v>462.22</v>
-      </c>
+      <c r="D47"/>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
       </c>
-      <c r="H47" t="n">
-        <v>490</v>
-      </c>
+      <c r="H47"/>
       <c r="I47" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" t="n">
-        <v>42.78</v>
-      </c>
-      <c r="K47" t="n">
-        <v>27.78</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J47"/>
+      <c r="K47"/>
     </row>
     <row r="48">
       <c r="B48" s="6" t="s">
@@ -5137,24 +5093,20 @@
         <v>260</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>251.88</v>
+        <v>274.65</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="6" t="n">
-        <v>310</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F48" s="6"/>
       <c r="G48" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" s="6"/>
       <c r="I48" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="6" t="n">
-        <v>58.12</v>
-      </c>
+      <c r="J48" s="6"/>
       <c r="K48" s="6"/>
     </row>
     <row r="49">
@@ -5164,20 +5116,26 @@
       <c r="C49" t="s">
         <v>273</v>
       </c>
-      <c r="D49"/>
+      <c r="D49" t="n">
+        <v>314.84</v>
+      </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49"/>
       <c r="G49" t="n">
         <v>0</v>
       </c>
-      <c r="H49"/>
+      <c r="H49" t="n">
+        <v>365</v>
+      </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49"/>
-      <c r="K49"/>
+      <c r="K49" t="n">
+        <v>50.16</v>
+      </c>
     </row>
     <row r="50">
       <c r="B50" s="6" t="s">
@@ -5186,11 +5144,9 @@
       <c r="C50" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="D50" s="6" t="n">
-        <v>281.35</v>
-      </c>
+      <c r="D50" s="6"/>
       <c r="E50" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="6" t="n">
@@ -5210,26 +5166,20 @@
       <c r="C51" t="s">
         <v>289</v>
       </c>
-      <c r="D51" t="n">
-        <v>291.4</v>
-      </c>
+      <c r="D51"/>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F51"/>
       <c r="G51" t="n">
         <v>0</v>
       </c>
-      <c r="H51" t="n">
-        <v>330</v>
-      </c>
+      <c r="H51"/>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51"/>
-      <c r="K51" t="n">
-        <v>38.6</v>
-      </c>
+      <c r="K51"/>
     </row>
     <row r="52">
       <c r="B52" s="6" t="s">
@@ -5242,9 +5192,11 @@
       <c r="E52" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F52" s="6"/>
+      <c r="F52" s="6" t="n">
+        <v>345</v>
+      </c>
       <c r="G52" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52" s="6"/>
       <c r="I52" s="6" t="n">
@@ -5264,11 +5216,9 @@
       <c r="E53" t="n">
         <v>0</v>
       </c>
-      <c r="F53" t="n">
-        <v>340</v>
-      </c>
+      <c r="F53"/>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53"/>
       <c r="I53" t="n">
@@ -5284,21 +5234,25 @@
       <c r="C54" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="D54" s="6"/>
+      <c r="D54" s="6" t="n">
+        <v>223.29</v>
+      </c>
       <c r="E54" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>246.67</v>
+        <v>257.5</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H54" s="6"/>
       <c r="I54" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="6"/>
+      <c r="J54" s="6" t="n">
+        <v>34.21</v>
+      </c>
       <c r="K54" s="6"/>
     </row>
     <row r="55">
@@ -5309,24 +5263,24 @@
         <v>273</v>
       </c>
       <c r="D55" t="n">
-        <v>219.72</v>
+        <v>251.88</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55"/>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>265</v>
+        <v>287.5</v>
       </c>
       <c r="I55" t="n">
         <v>2</v>
       </c>
       <c r="J55"/>
       <c r="K55" t="n">
-        <v>45.28</v>
+        <v>35.62</v>
       </c>
     </row>
     <row r="56">
@@ -5336,26 +5290,20 @@
       <c r="C56" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="D56" s="6" t="n">
-        <v>241.16</v>
-      </c>
+      <c r="D56" s="6"/>
       <c r="E56" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" s="6"/>
       <c r="G56" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="6" t="n">
-        <v>270</v>
-      </c>
+      <c r="H56" s="6"/>
       <c r="I56" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" s="6"/>
-      <c r="K56" s="6" t="n">
-        <v>28.84</v>
-      </c>
+      <c r="K56" s="6"/>
     </row>
     <row r="57">
       <c r="B57" t="s">
@@ -5368,17 +5316,13 @@
       <c r="E57" t="n">
         <v>0</v>
       </c>
-      <c r="F57" t="n">
-        <v>279.35</v>
-      </c>
+      <c r="F57"/>
       <c r="G57" t="n">
-        <v>3</v>
-      </c>
-      <c r="H57" t="n">
-        <v>275</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H57"/>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57"/>
       <c r="K57"/>
@@ -5390,26 +5334,22 @@
       <c r="C58" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="D58" s="6" t="n">
-        <v>241.16</v>
-      </c>
+      <c r="D58" s="6"/>
       <c r="E58" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J58" s="6"/>
-      <c r="K58" s="6" t="n">
-        <v>28.84</v>
-      </c>
+      <c r="K58" s="6"/>
     </row>
     <row r="59">
       <c r="B59" t="s">
@@ -5419,24 +5359,24 @@
         <v>300</v>
       </c>
       <c r="D59" t="n">
-        <v>235.8</v>
+        <v>225.08</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59"/>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>260</v>
+        <v>271.67</v>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J59"/>
       <c r="K59" t="n">
-        <v>24.2</v>
+        <v>46.59</v>
       </c>
     </row>
     <row r="60">
@@ -5446,19 +5386,19 @@
       <c r="C60" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="D60" s="6" t="n">
-        <v>182.21</v>
-      </c>
+      <c r="D60" s="6"/>
       <c r="E60" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60" s="6"/>
       <c r="G60" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="6"/>
+      <c r="H60" s="6" t="n">
+        <v>235</v>
+      </c>
       <c r="I60" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" s="6"/>
       <c r="K60" s="6"/>
@@ -5470,22 +5410,30 @@
       <c r="C61" t="s">
         <v>273</v>
       </c>
-      <c r="D61"/>
+      <c r="D61" t="n">
+        <v>206.32</v>
+      </c>
       <c r="E61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61"/>
+        <v>1</v>
+      </c>
+      <c r="F61" t="n">
+        <v>254.56</v>
+      </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="I61" t="n">
         <v>1</v>
       </c>
-      <c r="J61"/>
-      <c r="K61"/>
+      <c r="J61" t="n">
+        <v>48.24</v>
+      </c>
+      <c r="K61" t="n">
+        <v>38.68</v>
+      </c>
     </row>
     <row r="62">
       <c r="B62" s="6" t="s">
@@ -5494,19 +5442,25 @@
       <c r="C62" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="D62" s="6"/>
+      <c r="D62" s="6" t="n">
+        <v>206.32</v>
+      </c>
       <c r="E62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="6"/>
+        <v>1</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>250</v>
+      </c>
       <c r="G62" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" s="6"/>
       <c r="I62" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J62" s="6"/>
+      <c r="J62" s="6" t="n">
+        <v>43.68</v>
+      </c>
       <c r="K62" s="6"/>
     </row>
     <row r="63">
@@ -5517,25 +5471,25 @@
         <v>289</v>
       </c>
       <c r="D63" t="n">
-        <v>184.89</v>
+        <v>208.11</v>
       </c>
       <c r="E63" t="n">
+        <v>3</v>
+      </c>
+      <c r="F63"/>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>240</v>
+      </c>
+      <c r="I63" t="n">
         <v>1</v>
       </c>
-      <c r="F63" t="n">
-        <v>230</v>
-      </c>
-      <c r="G63" t="n">
-        <v>1</v>
-      </c>
-      <c r="H63"/>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="n">
-        <v>45.11</v>
-      </c>
-      <c r="K63"/>
+      <c r="J63"/>
+      <c r="K63" t="n">
+        <v>31.89</v>
+      </c>
     </row>
     <row r="64">
       <c r="B64" s="6" t="s">
@@ -5566,11 +5520,9 @@
       <c r="C65" t="s">
         <v>300</v>
       </c>
-      <c r="D65" t="n">
-        <v>171.49</v>
-      </c>
+      <c r="D65"/>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65"/>
       <c r="G65" t="n">
@@ -5604,7 +5556,7 @@
     </row>
     <row r="3">
       <c r="B3" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="4">
@@ -5623,83 +5575,83 @@
         <v>347</v>
       </c>
       <c r="C5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
+        <v>434</v>
+      </c>
+      <c r="E5" t="s">
+        <v>435</v>
+      </c>
+      <c r="F5" t="s">
+        <v>436</v>
+      </c>
+      <c r="G5" t="s">
         <v>437</v>
       </c>
-      <c r="E5" t="s">
+      <c r="H5" t="s">
         <v>438</v>
       </c>
-      <c r="F5" t="s">
+      <c r="I5" t="s">
         <v>439</v>
       </c>
-      <c r="G5" t="s">
+      <c r="J5" t="s">
         <v>440</v>
-      </c>
-      <c r="H5" t="s">
-        <v>441</v>
-      </c>
-      <c r="I5" t="s">
-        <v>442</v>
-      </c>
-      <c r="J5" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>128</v>
-      </c>
       <c r="D6" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>14.354</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="J6" s="6" t="s">
         <v>444</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>10.721</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>0.0299</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7" t="s">
         <v>131</v>
       </c>
-      <c r="C7" t="s">
-        <v>132</v>
-      </c>
       <c r="D7" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E7" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F7" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="G7" t="n">
-        <v>11.163</v>
+        <v>9.208</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0482</v>
+        <v>0.0561</v>
       </c>
       <c r="J7" t="s">
         <v>447</v>
@@ -5707,28 +5659,28 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>135</v>
-      </c>
       <c r="D8" s="6" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>6.121</v>
+        <v>2.402</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.0469</v>
+        <v>0.301</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>447</v>
@@ -5742,25 +5694,25 @@
         <v>138</v>
       </c>
       <c r="D9" t="s">
+        <v>441</v>
+      </c>
+      <c r="E9" t="s">
+        <v>450</v>
+      </c>
+      <c r="F9" t="s">
+        <v>451</v>
+      </c>
+      <c r="G9" t="n">
+        <v>7.887</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="J9" t="s">
         <v>444</v>
-      </c>
-      <c r="E9" t="s">
-        <v>452</v>
-      </c>
-      <c r="F9" t="s">
-        <v>453</v>
-      </c>
-      <c r="G9" t="n">
-        <v>7.741</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0517</v>
-      </c>
-      <c r="J9" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="10">
@@ -5771,25 +5723,25 @@
         <v>141</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>12.2</v>
+        <v>11.931</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>4</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.0159</v>
+        <v>0.0179</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="11">
@@ -5800,25 +5752,25 @@
         <v>144</v>
       </c>
       <c r="D11" t="s">
+        <v>441</v>
+      </c>
+      <c r="E11" t="s">
+        <v>454</v>
+      </c>
+      <c r="F11" t="s">
+        <v>455</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9.598</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.0223</v>
+      </c>
+      <c r="J11" t="s">
         <v>444</v>
-      </c>
-      <c r="E11" t="s">
-        <v>457</v>
-      </c>
-      <c r="F11" t="s">
-        <v>458</v>
-      </c>
-      <c r="G11" t="n">
-        <v>6.885</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="J11" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="12">
@@ -5829,19 +5781,19 @@
         <v>147</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="13">
@@ -5852,19 +5804,19 @@
         <v>150</v>
       </c>
       <c r="D13" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G13"/>
       <c r="H13"/>
       <c r="I13"/>
       <c r="J13" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="14">
@@ -5875,19 +5827,19 @@
         <v>154</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="15">
@@ -5898,19 +5850,19 @@
         <v>158</v>
       </c>
       <c r="D15" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G15"/>
       <c r="H15"/>
       <c r="I15"/>
       <c r="J15" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -5934,7 +5886,7 @@
     </row>
     <row r="3">
       <c r="B3" s="4" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="4">
@@ -5948,22 +5900,22 @@
     </row>
     <row r="5">
       <c r="B5" t="s">
+        <v>459</v>
+      </c>
+      <c r="C5" t="s">
+        <v>460</v>
+      </c>
+      <c r="D5" t="s">
+        <v>461</v>
+      </c>
+      <c r="E5" t="s">
         <v>462</v>
       </c>
-      <c r="C5" t="s">
+      <c r="F5" t="s">
         <v>463</v>
       </c>
-      <c r="D5" t="s">
+      <c r="G5" t="s">
         <v>464</v>
-      </c>
-      <c r="E5" t="s">
-        <v>465</v>
-      </c>
-      <c r="F5" t="s">
-        <v>466</v>
-      </c>
-      <c r="G5" t="s">
-        <v>467</v>
       </c>
       <c r="H5" t="s">
         <v>347</v>
@@ -5977,65 +5929,65 @@
         <v>294</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>-3.252</v>
+        <v>-3.437</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0.0011</v>
+        <v>0.0006</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.0115</v>
+        <v>0.0088</v>
       </c>
       <c r="G6" s="6" t="b">
         <v>1</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>260</v>
+        <v>294</v>
       </c>
       <c r="C7" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.937</v>
+        <v>2.716</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0528</v>
+        <v>0.0066</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4752</v>
+        <v>0.0924</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>294</v>
-      </c>
       <c r="D8" s="6" t="n">
-        <v>-1.769</v>
+        <v>-1.987</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>0.0769</v>
+        <v>0.0469</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.6156</v>
+        <v>0.6094</v>
       </c>
       <c r="G8" s="6" t="b">
         <v>0</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9">
@@ -6046,88 +5998,88 @@
         <v>289</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.655</v>
+        <v>-1.789</v>
       </c>
       <c r="E9" t="n">
-        <v>0.098</v>
+        <v>0.0736</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6861</v>
+        <v>0.8829</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>-1.598</v>
+        <v>-1.769</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>0.1101</v>
+        <v>0.0769</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.6861</v>
+        <v>0.8829</v>
       </c>
       <c r="G10" s="6" t="b">
         <v>0</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="C11" t="s">
         <v>294</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.491</v>
+        <v>-1.75</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1358</v>
+        <v>0.0801</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6861</v>
+        <v>0.8829</v>
       </c>
       <c r="G11" t="b">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>-1.483</v>
+        <v>1.443</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>0.138</v>
+        <v>0.149</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.6861</v>
+        <v>1</v>
       </c>
       <c r="G12" s="6" t="b">
         <v>0</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -6135,13 +6087,13 @@
         <v>273</v>
       </c>
       <c r="C13" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.373</v>
+        <v>-1.375</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7092</v>
+        <v>0.169</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -6150,7 +6102,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -6158,13 +6110,13 @@
         <v>283</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.192</v>
+        <v>-1.327</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>0.8474</v>
+        <v>0.1844</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>1</v>
@@ -6173,21 +6125,21 @@
         <v>0</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="C15" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.171</v>
+        <v>1.299</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8641</v>
+        <v>0.1938</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -6196,53 +6148,53 @@
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>260</v>
+        <v>289</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>-2.828</v>
+        <v>1.233</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>0.0047</v>
+        <v>0.2175</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.0702</v>
+        <v>1</v>
       </c>
       <c r="G16" s="6" t="b">
         <v>0</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="s">
-        <v>294</v>
+        <v>260</v>
       </c>
       <c r="C17" t="s">
         <v>300</v>
       </c>
       <c r="D17" t="n">
-        <v>2.548</v>
+        <v>-0.316</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0108</v>
+        <v>0.7517</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1518</v>
+        <v>1</v>
       </c>
       <c r="G17" t="b">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18">
@@ -6250,160 +6202,160 @@
         <v>273</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>-2.171</v>
+        <v>0.3</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>0.0299</v>
+        <v>0.7638</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.3893</v>
+        <v>1</v>
       </c>
       <c r="G18" s="6" t="b">
         <v>0</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="s">
+        <v>283</v>
+      </c>
+      <c r="C19" t="s">
         <v>289</v>
       </c>
-      <c r="C19" t="s">
-        <v>294</v>
-      </c>
       <c r="D19" t="n">
-        <v>-2.171</v>
+        <v>0.22</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0299</v>
+        <v>0.8262</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3893</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>283</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>-1.786</v>
+        <v>0.054</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.074</v>
+        <v>0.9569</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.8144</v>
+        <v>1</v>
       </c>
       <c r="G20" s="6" t="b">
         <v>0</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="s">
+        <v>260</v>
+      </c>
+      <c r="C21" t="s">
         <v>283</v>
       </c>
-      <c r="C21" t="s">
-        <v>300</v>
-      </c>
       <c r="D21" t="n">
-        <v>1.526</v>
+        <v>-2.602</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1271</v>
+        <v>0.0093</v>
       </c>
       <c r="F21" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="G21" t="b">
         <v>1</v>
       </c>
-      <c r="G21" t="b">
-        <v>0</v>
-      </c>
       <c r="H21" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>-1.186</v>
+        <v>2.191</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>0.2358</v>
+        <v>0.0284</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1</v>
+        <v>0.0569</v>
       </c>
       <c r="G22" s="6" t="b">
         <v>0</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>283</v>
+        <v>260</v>
       </c>
       <c r="C23" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="D23" t="n">
-        <v>1.186</v>
+        <v>-0.709</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2358</v>
+        <v>0.4784</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0.4784</v>
       </c>
       <c r="G23" t="b">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>294</v>
-      </c>
       <c r="D24" s="6" t="n">
-        <v>-1.135</v>
+        <v>-2.682</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>0.2563</v>
+        <v>0.0073</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>1</v>
+        <v>0.0731</v>
       </c>
       <c r="G24" s="6" t="b">
         <v>0</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25">
@@ -6411,22 +6363,22 @@
         <v>260</v>
       </c>
       <c r="C25" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.401</v>
+        <v>-2.604</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6884</v>
+        <v>0.0092</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0.0829</v>
       </c>
       <c r="G25" t="b">
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26">
@@ -6434,45 +6386,45 @@
         <v>260</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>-0.401</v>
+        <v>-2.459</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>0.6884</v>
+        <v>0.0139</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>1</v>
+        <v>0.1114</v>
       </c>
       <c r="G26" s="6" t="b">
         <v>0</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="C27" t="s">
         <v>300</v>
       </c>
       <c r="D27" t="n">
-        <v>0.227</v>
+        <v>1.915</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8204</v>
+        <v>0.0555</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0.3887</v>
       </c>
       <c r="G27" t="b">
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28">
@@ -6483,56 +6435,56 @@
         <v>300</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0.227</v>
+        <v>1.73</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>0.8204</v>
+        <v>0.0836</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>1</v>
+        <v>0.5018</v>
       </c>
       <c r="G28" s="6" t="b">
         <v>0</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="s">
-        <v>260</v>
+        <v>294</v>
       </c>
       <c r="C29" t="s">
         <v>300</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.178</v>
+        <v>1.585</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8587</v>
+        <v>0.1129</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0.5645</v>
       </c>
       <c r="G29" t="b">
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="6" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>0</v>
+        <v>-0.829</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>1</v>
+        <v>0.407</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>1</v>
@@ -6541,30 +6493,30 @@
         <v>0</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="s">
+        <v>283</v>
+      </c>
+      <c r="C31" t="s">
         <v>294</v>
       </c>
-      <c r="C31" t="s">
-        <v>300</v>
-      </c>
       <c r="D31" t="n">
-        <v>2.209</v>
+        <v>0.546</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0271</v>
+        <v>0.5849</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0814</v>
+        <v>1</v>
       </c>
       <c r="G31" t="b">
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32">
@@ -6572,160 +6524,160 @@
         <v>283</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>-2.05</v>
+        <v>0.413</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>0.0404</v>
+        <v>0.6793</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.0814</v>
+        <v>1</v>
       </c>
       <c r="G32" s="6" t="b">
         <v>0</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="C33" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.114</v>
+        <v>0.153</v>
       </c>
       <c r="E33" t="n">
-        <v>0.909</v>
+        <v>0.878</v>
       </c>
       <c r="F33" t="n">
-        <v>0.909</v>
+        <v>1</v>
       </c>
       <c r="G33" t="b">
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>2.883</v>
+        <v>-2.593</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>0.0039</v>
+        <v>0.0095</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0.0394</v>
+        <v>0.0572</v>
       </c>
       <c r="G34" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="s">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="C35" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="D35" t="n">
-        <v>2.669</v>
+        <v>2.13</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0076</v>
+        <v>0.0332</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0685</v>
+        <v>0.1658</v>
       </c>
       <c r="G35" t="b">
         <v>0</v>
       </c>
       <c r="H35" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="6" t="s">
-        <v>283</v>
+        <v>260</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>2.017</v>
+        <v>-2.049</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.0437</v>
+        <v>0.0405</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.3498</v>
+        <v>0.1658</v>
       </c>
       <c r="G36" s="6" t="b">
         <v>0</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="s">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="C37" t="s">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.887</v>
+        <v>-1.695</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0592</v>
+        <v>0.0901</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4145</v>
+        <v>0.2703</v>
       </c>
       <c r="G37" t="b">
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="6" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>1.53</v>
+        <v>0.318</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>0.1261</v>
+        <v>0.7503</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>0.7567</v>
+        <v>1</v>
       </c>
       <c r="G38" s="6" t="b">
         <v>0</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="39">
@@ -6733,13 +6685,13 @@
         <v>273</v>
       </c>
       <c r="C39" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.07</v>
+        <v>-0.154</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2848</v>
+        <v>0.8779</v>
       </c>
       <c r="F39" t="n">
         <v>1</v>
@@ -6748,167 +6700,6 @@
         <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="D40" s="6" t="n">
-        <v>-1.019</v>
-      </c>
-      <c r="E40" s="6" t="n">
-        <v>0.3083</v>
-      </c>
-      <c r="F40" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" t="s">
-        <v>273</v>
-      </c>
-      <c r="C41" t="s">
-        <v>289</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.797</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.4252</v>
-      </c>
-      <c r="F41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="D42" s="6" t="n">
-        <v>0.757</v>
-      </c>
-      <c r="E42" s="6" t="n">
-        <v>0.4489</v>
-      </c>
-      <c r="F42" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" t="s">
-        <v>283</v>
-      </c>
-      <c r="C43" t="s">
-        <v>294</v>
-      </c>
-      <c r="D43" t="n">
-        <v>-0.019</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0.9845</v>
-      </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="D44" s="6" t="n">
-        <v>-2.509</v>
-      </c>
-      <c r="E44" s="6" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="F44" s="6" t="n">
-        <v>0.0363</v>
-      </c>
-      <c r="G44" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" t="s">
-        <v>260</v>
-      </c>
-      <c r="C45" t="s">
-        <v>289</v>
-      </c>
-      <c r="D45" t="n">
-        <v>-1.919</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G45" t="b">
-        <v>0</v>
-      </c>
-      <c r="H45" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" t="s">
-        <v>283</v>
-      </c>
-      <c r="C46" t="s">
-        <v>289</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0.5549</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.5549</v>
-      </c>
-      <c r="G46" t="b">
-        <v>0</v>
-      </c>
-      <c r="H46" t="s">
         <v>143</v>
       </c>
     </row>
@@ -6933,7 +6724,7 @@
     </row>
     <row r="3">
       <c r="B3" s="4" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
     </row>
     <row r="4">
@@ -6952,16 +6743,16 @@
         <v>48</v>
       </c>
       <c r="D5" t="s">
+        <v>466</v>
+      </c>
+      <c r="E5" t="s">
+        <v>467</v>
+      </c>
+      <c r="F5" t="s">
+        <v>468</v>
+      </c>
+      <c r="G5" t="s">
         <v>469</v>
-      </c>
-      <c r="E5" t="s">
-        <v>470</v>
-      </c>
-      <c r="F5" t="s">
-        <v>471</v>
-      </c>
-      <c r="G5" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="6">
@@ -6972,16 +6763,16 @@
         <v>30</v>
       </c>
       <c r="D6" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E6" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="E6" s="6" t="n">
-        <v>13</v>
-      </c>
       <c r="F6" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="7">
@@ -6992,16 +6783,16 @@
         <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="8">
@@ -7012,21 +6803,21 @@
         <v>30</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>3</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C9" t="n">
         <v>90</v>
@@ -7035,19 +6826,19 @@
       <c r="E9"/>
       <c r="F9"/>
       <c r="G9" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C10"/>
       <c r="D10"/>
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
   </sheetData>
@@ -7130,31 +6921,31 @@
         <v>30</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>44.13</v>
+        <v>47.1</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>10.52</v>
+        <v>9.49</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>18.73</v>
+        <v>20.63</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>8.61</v>
+        <v>9.17</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>6.13</v>
+        <v>5.9</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>23.3</v>
+        <v>13.3</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>23.3</v>
+        <v>36.7</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>26.7</v>
+        <v>43.3</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>26.7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="7">
@@ -7162,34 +6953,34 @@
         <v>59</v>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>40.1</v>
+        <v>39.82</v>
       </c>
       <c r="E7" t="n">
-        <v>9.73</v>
+        <v>11.4</v>
       </c>
       <c r="F7" t="n">
-        <v>15.85</v>
+        <v>16.23</v>
       </c>
       <c r="G7" t="n">
-        <v>9.4</v>
+        <v>9.04</v>
       </c>
       <c r="H7" t="n">
-        <v>4.65</v>
+        <v>4.73</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="J7" t="n">
-        <v>65</v>
+        <v>36.4</v>
       </c>
       <c r="K7" t="n">
-        <v>30</v>
+        <v>40.9</v>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="8">
@@ -7197,34 +6988,34 @@
         <v>60</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>40.4</v>
+        <v>45.38</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>12.19</v>
+        <v>9.24</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>17.9</v>
+        <v>16.38</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>10.44</v>
+        <v>5.76</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>4.3</v>
+        <v>4.62</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>50</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -7235,28 +7026,28 @@
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>38.77</v>
+        <v>38.63</v>
       </c>
       <c r="E9" t="n">
-        <v>11.31</v>
+        <v>10.01</v>
       </c>
       <c r="F9" t="n">
-        <v>12.77</v>
+        <v>11.43</v>
       </c>
       <c r="G9" t="n">
-        <v>7.95</v>
+        <v>7.43</v>
       </c>
       <c r="H9" t="n">
-        <v>4.7</v>
+        <v>5.43</v>
       </c>
       <c r="I9" t="n">
-        <v>23.3</v>
+        <v>16.7</v>
       </c>
       <c r="J9" t="n">
-        <v>23.3</v>
+        <v>36.7</v>
       </c>
       <c r="K9" t="n">
-        <v>43.3</v>
+        <v>36.7</v>
       </c>
       <c r="L9" t="n">
         <v>10</v>
@@ -7270,31 +7061,31 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>41.03</v>
+        <v>42.34</v>
       </c>
       <c r="E10" t="n">
-        <v>10.87</v>
+        <v>10.68</v>
       </c>
       <c r="F10" t="n">
-        <v>16.01</v>
+        <v>16.11</v>
       </c>
       <c r="G10" t="n">
-        <v>9.01</v>
+        <v>9.03</v>
       </c>
       <c r="H10" t="n">
-        <v>5.12</v>
+        <v>5.34</v>
       </c>
       <c r="I10" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="J10" t="n">
-        <v>33.3</v>
+        <v>37.8</v>
       </c>
       <c r="K10" t="n">
-        <v>35.6</v>
+        <v>41.1</v>
       </c>
       <c r="L10" t="n">
-        <v>14.4</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -7318,7 +7109,7 @@
     </row>
     <row r="3">
       <c r="B3" s="4" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
     <row r="4">
@@ -7336,13 +7127,13 @@
         <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="E5" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="F5" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
     </row>
     <row r="6">
@@ -7350,33 +7141,33 @@
         <v>58</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>30.14</v>
+        <v>33.5</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>9.63</v>
+        <v>8.42</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="C7" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="D7" t="n">
-        <v>83.74</v>
+        <v>81.22</v>
       </c>
       <c r="E7" t="n">
-        <v>20.26</v>
+        <v>30.21</v>
       </c>
       <c r="F7" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8">
@@ -7384,55 +7175,55 @@
         <v>370</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>182</v>
+        <v>172.5</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>45.88</v>
+        <v>62.23</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C9" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
       <c r="F9" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C11" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
       <c r="F11" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -7456,7 +7247,7 @@
     </row>
     <row r="3">
       <c r="B3" s="4" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="4">
@@ -7468,381 +7259,381 @@
     </row>
     <row r="5">
       <c r="B5" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="C5" t="s">
         <v>243</v>
       </c>
       <c r="D5" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="E5" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="F5" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>369</v>
+        <v>495</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>260</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>200</v>
+        <v>127</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>4.42</v>
+        <v>8.62</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>195.58</v>
+        <v>118.38</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C7" t="s">
         <v>260</v>
       </c>
       <c r="D7" t="n">
-        <v>218.75</v>
+        <v>128</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>2.6</v>
       </c>
       <c r="F7" t="n">
-        <v>210.75</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>260</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>148.33</v>
+        <v>173.75</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>5.82</v>
+        <v>12.67</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>142.51</v>
+        <v>161.08</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="s">
-        <v>373</v>
+        <v>497</v>
       </c>
       <c r="C9" t="s">
         <v>260</v>
       </c>
       <c r="D9" t="n">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="E9" t="n">
-        <v>5.06</v>
+        <v>4.62</v>
       </c>
       <c r="F9" t="n">
-        <v>169.94</v>
+        <v>179.38</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>500</v>
+        <v>369</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>260</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>158.75</v>
+        <v>148.71</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>2.94</v>
+        <v>5.31</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>155.81</v>
+        <v>143.41</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>501</v>
+        <v>382</v>
       </c>
       <c r="C11" t="s">
         <v>273</v>
       </c>
       <c r="D11" t="n">
-        <v>198.33</v>
+        <v>248.33</v>
       </c>
       <c r="E11" t="n">
-        <v>8.47</v>
+        <v>10.49</v>
       </c>
       <c r="F11" t="n">
-        <v>189.86</v>
+        <v>237.84</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>379</v>
+        <v>498</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>273</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>115</v>
+        <v>74.69</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>111.33</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="s">
-        <v>502</v>
+        <v>376</v>
       </c>
       <c r="C13" t="s">
         <v>273</v>
       </c>
       <c r="D13" t="n">
-        <v>184</v>
+        <v>144.69</v>
       </c>
       <c r="E13" t="n">
-        <v>8.5</v>
+        <v>5.95</v>
       </c>
       <c r="F13" t="n">
-        <v>175.5</v>
+        <v>138.74</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>273</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>160</v>
+        <v>221.06</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>3.62</v>
+        <v>4.93</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>156.38</v>
+        <v>216.14</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C15" t="s">
         <v>273</v>
       </c>
       <c r="D15" t="n">
-        <v>197.5</v>
+        <v>246.18</v>
       </c>
       <c r="E15" t="n">
-        <v>4.12</v>
+        <v>5.56</v>
       </c>
       <c r="F15" t="n">
-        <v>193.38</v>
+        <v>240.62</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>385</v>
+        <v>500</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>283</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>205</v>
+        <v>107.5</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>5.38</v>
+        <v>2.47</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>199.62</v>
+        <v>105.03</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="s">
-        <v>389</v>
+        <v>501</v>
       </c>
       <c r="C17" t="s">
         <v>283</v>
       </c>
       <c r="D17" t="n">
-        <v>154</v>
+        <v>207.67</v>
       </c>
       <c r="E17" t="n">
-        <v>4.24</v>
+        <v>5.69</v>
       </c>
       <c r="F17" t="n">
-        <v>149.76</v>
+        <v>201.97</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>504</v>
+        <v>385</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>283</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>201</v>
+        <v>208.75</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>3.4</v>
+        <v>3.81</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>197.6</v>
+        <v>204.94</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="s">
-        <v>505</v>
+        <v>388</v>
       </c>
       <c r="C19" t="s">
         <v>283</v>
       </c>
       <c r="D19" t="n">
-        <v>192.5</v>
+        <v>306.67</v>
       </c>
       <c r="E19" t="n">
-        <v>4.23</v>
+        <v>3.63</v>
       </c>
       <c r="F19" t="n">
-        <v>188.27</v>
+        <v>303.04</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>283</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>6.07</v>
+        <v>2.99</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>177.93</v>
+        <v>210.01</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="s">
-        <v>507</v>
+        <v>391</v>
       </c>
       <c r="C21" t="s">
         <v>289</v>
       </c>
       <c r="D21" t="n">
-        <v>132.5</v>
+        <v>180.87</v>
       </c>
       <c r="E21" t="n">
-        <v>3.16</v>
+        <v>9.01</v>
       </c>
       <c r="F21" t="n">
-        <v>129.34</v>
+        <v>171.86</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>508</v>
+        <v>395</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>289</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>133.33</v>
+        <v>204</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>3.02</v>
+        <v>6</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>130.31</v>
+        <v>198</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>392</v>
+        <v>503</v>
       </c>
       <c r="C23" t="s">
         <v>289</v>
       </c>
       <c r="D23" t="n">
-        <v>179</v>
+        <v>146</v>
       </c>
       <c r="E23" t="n">
-        <v>4.13</v>
+        <v>2.88</v>
       </c>
       <c r="F23" t="n">
-        <v>174.87</v>
+        <v>143.12</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>289</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>5.1</v>
+        <v>11.81</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>145.9</v>
+        <v>143.19</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="s">
-        <v>395</v>
+        <v>505</v>
       </c>
       <c r="C25" t="s">
         <v>289</v>
       </c>
       <c r="D25" t="n">
-        <v>96.47</v>
+        <v>208</v>
       </c>
       <c r="E25" t="n">
-        <v>4.67</v>
+        <v>3.16</v>
       </c>
       <c r="F25" t="n">
-        <v>91.8</v>
+        <v>204.84</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>294</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>188.33</v>
+        <v>140</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>5.54</v>
+        <v>3.44</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>182.79</v>
+        <v>136.56</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="C27" t="s">
         <v>294</v>
@@ -7851,112 +7642,112 @@
         <v>171.25</v>
       </c>
       <c r="E27" t="n">
-        <v>4.71</v>
+        <v>7.86</v>
       </c>
       <c r="F27" t="n">
-        <v>166.54</v>
+        <v>163.39</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="s">
-        <v>398</v>
+        <v>507</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>294</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>202</v>
+        <v>98.75</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>4.37</v>
+        <v>8.12</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>197.63</v>
+        <v>90.62</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="s">
-        <v>511</v>
+        <v>398</v>
       </c>
       <c r="C29" t="s">
         <v>294</v>
       </c>
       <c r="D29" t="n">
-        <v>202.5</v>
+        <v>199</v>
       </c>
       <c r="E29" t="n">
-        <v>7.29</v>
+        <v>8.91</v>
       </c>
       <c r="F29" t="n">
-        <v>195.21</v>
+        <v>190.09</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="6" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>294</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>241.16</v>
+        <v>189</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>6.01</v>
+        <v>3.57</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>235.15</v>
+        <v>185.43</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="s">
-        <v>513</v>
+        <v>405</v>
       </c>
       <c r="C31" t="s">
         <v>300</v>
       </c>
       <c r="D31" t="n">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="E31" t="n">
-        <v>5.48</v>
+        <v>5.45</v>
       </c>
       <c r="F31" t="n">
-        <v>174.52</v>
+        <v>200.55</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>300</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>142</v>
+        <v>159.43</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>4.06</v>
+        <v>3.35</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>137.94</v>
+        <v>156.08</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="s">
-        <v>411</v>
+        <v>510</v>
       </c>
       <c r="C33" t="s">
         <v>300</v>
       </c>
       <c r="D33" t="n">
-        <v>157.5</v>
+        <v>165</v>
       </c>
       <c r="E33" t="n">
-        <v>3.2</v>
+        <v>2.28</v>
       </c>
       <c r="F33" t="n">
-        <v>154.3</v>
+        <v>162.72</v>
       </c>
     </row>
     <row r="34">
@@ -7967,45 +7758,45 @@
         <v>300</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>201.25</v>
+        <v>133.33</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>4.49</v>
+        <v>10.45</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>196.76</v>
+        <v>122.88</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="s">
-        <v>405</v>
+        <v>511</v>
       </c>
       <c r="C35" t="s">
         <v>300</v>
       </c>
       <c r="D35" t="n">
-        <v>210</v>
+        <v>155</v>
       </c>
       <c r="E35" t="n">
-        <v>4.85</v>
+        <v>4.52</v>
       </c>
       <c r="F35" t="n">
-        <v>205.15</v>
+        <v>150.48</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C36" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D36"/>
       <c r="E36" t="n">
-        <v>0.43</v>
+        <v>0.055</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0177</v>
+        <v>0.773</v>
       </c>
     </row>
   </sheetData>
@@ -8029,7 +7820,7 @@
     </row>
     <row r="3">
       <c r="B3" s="4" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="4">
@@ -8041,104 +7832,104 @@
     </row>
     <row r="5">
       <c r="B5" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C5" t="s">
         <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="E5" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F5" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.8544</v>
+        <v>0.9035</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0</v>
+        <v>0.0006</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C7" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8457</v>
+        <v>0.9046</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.0008</v>
       </c>
       <c r="F7" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.9076</v>
+        <v>0.8959</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="C9" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8967</v>
+        <v>0.8951</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C10" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8333</v>
+        <v>0.8123</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
   </sheetData>
@@ -8225,25 +8016,25 @@
         <v>30</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>797.4</v>
+        <v>801.14</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>272.75</v>
+        <v>328.39</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>821</v>
+        <v>839.7</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>373.2</v>
+        <v>298.6</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>1306.2</v>
+        <v>1268.9</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>5.37</v>
+        <v>5.47</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>636.67</v>
+        <v>673.33</v>
       </c>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
@@ -8257,27 +8048,27 @@
         <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>204.51</v>
+        <v>205.26</v>
       </c>
       <c r="E7" t="n">
-        <v>107.05</v>
+        <v>103.06</v>
       </c>
       <c r="F7" t="n">
-        <v>186.6</v>
+        <v>167.9</v>
       </c>
       <c r="G7" t="n">
-        <v>44.8</v>
+        <v>48.5</v>
       </c>
       <c r="H7" t="n">
-        <v>410.5</v>
+        <v>447.8</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
       <c r="K7" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="L7" t="n">
-        <v>79.97</v>
+        <v>73.57</v>
       </c>
       <c r="M7"/>
     </row>
@@ -8289,26 +8080,26 @@
         <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>99.95</v>
+        <v>95.94</v>
       </c>
       <c r="E8" t="n">
-        <v>27.47</v>
+        <v>35.07</v>
       </c>
       <c r="F8" t="n">
-        <v>103.5</v>
+        <v>102.6</v>
       </c>
       <c r="G8" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="H8" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
       <c r="L8"/>
       <c r="M8" t="n">
-        <v>5.43</v>
+        <v>5.53</v>
       </c>
     </row>
   </sheetData>
@@ -8332,7 +8123,7 @@
     </row>
     <row r="3">
       <c r="B3" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4">
@@ -8370,10 +8161,10 @@
         <v>59</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="7">
@@ -8387,10 +8178,10 @@
         <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
-        <v>33.3</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="8">
@@ -8404,10 +8195,10 @@
         <v>83</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>83.3</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="9">
@@ -8421,10 +8212,10 @@
         <v>84</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F9" t="n">
-        <v>16.7</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="10">
@@ -8438,10 +8229,10 @@
         <v>86</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>43.3</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="11">
@@ -8455,10 +8246,10 @@
         <v>58</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F11" t="n">
-        <v>40</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="12">
@@ -8472,10 +8263,10 @@
         <v>60</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="13">
@@ -8483,16 +8274,16 @@
         <v>80</v>
       </c>
       <c r="C13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" t="s">
         <v>87</v>
       </c>
-      <c r="D13" t="s">
-        <v>88</v>
-      </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>30</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="14">
@@ -8500,16 +8291,16 @@
         <v>80</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>89</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>16.7</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="15">
@@ -8517,16 +8308,16 @@
         <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
         <v>90</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -8534,16 +8325,16 @@
         <v>80</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>91</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="17">
@@ -8551,16 +8342,16 @@
         <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
         <v>92</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="18">
@@ -8568,7 +8359,7 @@
         <v>80</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>93</v>
@@ -8585,16 +8376,16 @@
         <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>6.7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -8602,7 +8393,7 @@
         <v>80</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>95</v>
@@ -8642,10 +8433,10 @@
         <v>98</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>70</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="23">
@@ -8659,10 +8450,10 @@
         <v>99</v>
       </c>
       <c r="E23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F23" t="n">
-        <v>26.7</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="24">
@@ -8676,10 +8467,10 @@
         <v>58</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>56.7</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="25">
@@ -8690,7 +8481,7 @@
         <v>101</v>
       </c>
       <c r="D25" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="E25" t="n">
         <v>5</v>
@@ -8707,13 +8498,13 @@
         <v>101</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>16.7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="27">
@@ -8724,13 +8515,13 @@
         <v>101</v>
       </c>
       <c r="D27" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>10</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="28">
@@ -8738,16 +8529,16 @@
         <v>100</v>
       </c>
       <c r="C28" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D28" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>104</v>
-      </c>
       <c r="E28" s="6" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>70</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="29">
@@ -8755,16 +8546,16 @@
         <v>100</v>
       </c>
       <c r="C29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D29" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F29" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="30">
@@ -8772,16 +8563,16 @@
         <v>100</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="31">
@@ -8789,16 +8580,16 @@
         <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D31" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>6.7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
@@ -8806,16 +8597,16 @@
         <v>100</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>3.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="33">
@@ -8823,16 +8614,16 @@
         <v>100</v>
       </c>
       <c r="C33" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D33" t="s">
         <v>97</v>
       </c>
       <c r="E33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F33" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="34">
@@ -8840,16 +8631,16 @@
         <v>100</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>98</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35">
@@ -8857,7 +8648,7 @@
         <v>100</v>
       </c>
       <c r="C35" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D35" t="s">
         <v>99</v>
@@ -8914,122 +8705,122 @@
     </row>
     <row r="5">
       <c r="B5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" t="s">
         <v>110</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>111</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>112</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>113</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>114</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>115</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>116</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>117</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>118</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>119</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>120</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>121</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O5" t="s">
         <v>122</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>123</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>124</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>125</v>
-      </c>
-      <c r="R5" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>129</v>
-      </c>
       <c r="E6" s="6" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>6</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>1031.62</v>
+        <v>1045.02</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>1083.3</v>
+        <v>1093.4</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>1236.41</v>
+        <v>1286.17</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>1486.96</v>
+        <v>1533.71</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>1420</v>
+        <v>1518</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>51.68</v>
+        <v>48.38</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>153.11</v>
+        <v>192.77</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>183.59</v>
+        <v>231.83</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>388.38</v>
+        <v>472.98</v>
       </c>
       <c r="R6" s="6" t="n">
-        <v>72.6</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7" t="s">
         <v>131</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>132</v>
       </c>
-      <c r="D7" t="s">
-        <v>133</v>
-      </c>
       <c r="E7" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F7" t="n">
         <v>6</v>
@@ -9038,91 +8829,81 @@
         <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I7" t="n">
-        <v>1110.67</v>
+        <v>1147.17</v>
       </c>
       <c r="J7" t="n">
-        <v>1165.59</v>
+        <v>1198.25</v>
       </c>
       <c r="K7" t="n">
-        <v>1378.04</v>
+        <v>1419.09</v>
       </c>
       <c r="L7" t="n">
-        <v>1619.16</v>
+        <v>1666.39</v>
       </c>
       <c r="M7" t="n">
-        <v>1615</v>
+        <v>1641.67</v>
       </c>
       <c r="N7" t="n">
-        <v>54.92</v>
+        <v>51.08</v>
       </c>
       <c r="O7" t="n">
-        <v>212.45</v>
+        <v>220.84</v>
       </c>
       <c r="P7" t="n">
-        <v>236.96</v>
+        <v>222.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>504.33</v>
+        <v>494.5</v>
       </c>
       <c r="R7" t="n">
-        <v>68.8</v>
+        <v>69.9</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="D8" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E8" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>130</v>
-      </c>
       <c r="I8" s="6" t="n">
-        <v>735.53</v>
+        <v>762.83</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>771.7</v>
+        <v>798.83</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>886.61</v>
+        <v>932.25</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>1069.64</v>
+        <v>1101.84</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>1033.33</v>
-      </c>
-      <c r="N8" s="6" t="n">
-        <v>36.17</v>
-      </c>
-      <c r="O8" s="6" t="n">
-        <v>114.91</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v>146.72</v>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v>297.8</v>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v>71.2</v>
-      </c>
+        <v>1015</v>
+      </c>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
     </row>
     <row r="9">
       <c r="B9" t="s">
@@ -9141,40 +8922,40 @@
         <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I9" t="n">
-        <v>660.95</v>
+        <v>651.13</v>
       </c>
       <c r="J9" t="n">
-        <v>687.75</v>
+        <v>681.94</v>
       </c>
       <c r="K9" t="n">
-        <v>762.77</v>
+        <v>801.47</v>
       </c>
       <c r="L9" t="n">
-        <v>933.44</v>
+        <v>937.02</v>
       </c>
       <c r="M9" t="n">
-        <v>885</v>
+        <v>911.67</v>
       </c>
       <c r="N9" t="n">
-        <v>26.8</v>
+        <v>30.81</v>
       </c>
       <c r="O9" t="n">
-        <v>75.02</v>
+        <v>119.53</v>
       </c>
       <c r="P9" t="n">
-        <v>122.23</v>
+        <v>110.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>224.05</v>
+        <v>260.54</v>
       </c>
       <c r="R9" t="n">
-        <v>74.7</v>
+        <v>71.4</v>
       </c>
     </row>
     <row r="10">
@@ -9188,46 +8969,46 @@
         <v>142</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>6</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>407.79</v>
+        <v>414.49</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>428.72</v>
+        <v>433.75</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>501.77</v>
+        <v>505.48</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>581.23</v>
+        <v>601.32</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>585</v>
+        <v>609.44</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>20.93</v>
+        <v>19.26</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>73.05</v>
+        <v>71.73</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>83.23</v>
+        <v>103.96</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>177.21</v>
+        <v>194.95</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>69.7</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11">
@@ -9241,46 +9022,46 @@
         <v>145</v>
       </c>
       <c r="E11" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F11" t="n">
         <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I11" t="n">
-        <v>314.1</v>
+        <v>320.42</v>
       </c>
       <c r="J11" t="n">
-        <v>323.55</v>
+        <v>333.82</v>
       </c>
       <c r="K11" t="n">
-        <v>380.42</v>
+        <v>400.1</v>
       </c>
       <c r="L11" t="n">
-        <v>457.13</v>
+        <v>483.74</v>
       </c>
       <c r="M11" t="n">
-        <v>446.54</v>
+        <v>461.11</v>
       </c>
       <c r="N11" t="n">
-        <v>9.45</v>
+        <v>13.4</v>
       </c>
       <c r="O11" t="n">
-        <v>56.87</v>
+        <v>66.28</v>
       </c>
       <c r="P11" t="n">
-        <v>66.12</v>
+        <v>61.01</v>
       </c>
       <c r="Q11" t="n">
-        <v>132.44</v>
+        <v>140.69</v>
       </c>
       <c r="R11" t="n">
-        <v>70.3</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="12">
@@ -9294,7 +9075,7 @@
         <v>148</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>5</v>
@@ -9303,37 +9084,37 @@
         <v>7</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>361.74</v>
+        <v>368.44</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>377.81</v>
+        <v>385.18</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>450.16</v>
+        <v>451.61</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>545.45</v>
+        <v>542.45</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>530</v>
+        <v>540.71</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>16.07</v>
+        <v>16.74</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>72.35</v>
+        <v>66.43</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>79.84</v>
+        <v>89.1</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>168.26</v>
+        <v>172.27</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>68.3</v>
+        <v>68.1</v>
       </c>
     </row>
     <row r="13">
@@ -9347,10 +9128,10 @@
         <v>151</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -9359,19 +9140,19 @@
         <v>152</v>
       </c>
       <c r="I13" t="n">
-        <v>231.78</v>
+        <v>257.23</v>
       </c>
       <c r="J13" t="n">
-        <v>241.16</v>
+        <v>267.95</v>
       </c>
       <c r="K13" t="n">
-        <v>279.01</v>
+        <v>288.05</v>
       </c>
       <c r="L13" t="n">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="M13" t="n">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="N13"/>
       <c r="O13"/>
@@ -9390,46 +9171,46 @@
         <v>155</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>156</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>188.91</v>
+        <v>202.31</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>195.61</v>
+        <v>211.68</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>234.46</v>
+        <v>231.97</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>263.01</v>
+        <v>257.5</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>267.5</v>
+        <v>282.5</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>6.7</v>
+        <v>9.37</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>38.85</v>
+        <v>20.29</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>33.04</v>
+        <v>50.53</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>78.59</v>
+        <v>80.19</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>70.6</v>
+        <v>71.6</v>
       </c>
     </row>
     <row r="15">
@@ -9443,29 +9224,27 @@
         <v>159</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15" t="s">
         <v>160</v>
       </c>
-      <c r="I15" t="n">
-        <v>163.45</v>
-      </c>
+      <c r="I15"/>
       <c r="J15"/>
       <c r="K15" t="n">
-        <v>179.53</v>
+        <v>207.39</v>
       </c>
       <c r="L15" t="n">
-        <v>230</v>
+        <v>252.28</v>
       </c>
       <c r="M15" t="n">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="N15"/>
       <c r="O15"/>
@@ -9484,7 +9263,7 @@
         <v>163</v>
       </c>
       <c r="E16" t="n">
-        <v>414</v>
+        <v>368</v>
       </c>
       <c r="F16"/>
       <c r="G16"/>
@@ -9492,34 +9271,34 @@
         <v>164</v>
       </c>
       <c r="I16" t="n">
-        <v>601.41</v>
+        <v>592.71</v>
       </c>
       <c r="J16" t="n">
-        <v>629.25</v>
+        <v>619.72</v>
       </c>
       <c r="K16" t="n">
-        <v>728.83</v>
+        <v>727.98</v>
       </c>
       <c r="L16" t="n">
-        <v>869.5</v>
+        <v>860.3</v>
       </c>
       <c r="M16" t="n">
-        <v>847.8</v>
+        <v>852.16</v>
       </c>
       <c r="N16" t="n">
-        <v>27.84</v>
+        <v>27.01</v>
       </c>
       <c r="O16" t="n">
-        <v>99.58</v>
+        <v>108.26</v>
       </c>
       <c r="P16" t="n">
-        <v>118.97</v>
+        <v>124.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>246.39</v>
+        <v>259.45</v>
       </c>
       <c r="R16" t="n">
-        <v>70.9</v>
+        <v>69.6</v>
       </c>
     </row>
   </sheetData>
@@ -9589,13 +9368,13 @@
         <v>172</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>3.34</v>
+        <v>2.92</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1.06</v>
+        <v>0.83</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>173</v>
@@ -9615,13 +9394,13 @@
         <v>18</v>
       </c>
       <c r="F7" t="n">
-        <v>184444.44</v>
+        <v>187222.22</v>
       </c>
       <c r="G7" t="n">
-        <v>64986.17</v>
+        <v>109063.15</v>
       </c>
       <c r="H7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8">
@@ -9638,13 +9417,13 @@
         <v>12</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>19583.33</v>
+        <v>10291.67</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>9440.8</v>
+        <v>9321.18</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9">
@@ -9658,16 +9437,16 @@
         <v>177</v>
       </c>
       <c r="E9" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F9" t="n">
-        <v>8330.77</v>
+        <v>7937.93</v>
       </c>
       <c r="G9" t="n">
-        <v>3205.84</v>
+        <v>3302.86</v>
       </c>
       <c r="H9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10">
@@ -9681,16 +9460,16 @@
         <v>175</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>9025</v>
+        <v>7600</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>2223.17</v>
+        <v>0</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11">
@@ -9707,10 +9486,10 @@
         <v>30</v>
       </c>
       <c r="F11" t="n">
-        <v>5.37</v>
+        <v>5.47</v>
       </c>
       <c r="G11" t="n">
-        <v>2.47</v>
+        <v>2.26</v>
       </c>
       <c r="H11" t="s">
         <v>182</v>
@@ -9730,13 +9509,13 @@
         <v>30</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>636.67</v>
+        <v>673.33</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>122.43</v>
+        <v>93.53</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
@@ -9750,16 +9529,16 @@
         <v>175</v>
       </c>
       <c r="E13" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F13" t="n">
-        <v>6093.75</v>
+        <v>6700</v>
       </c>
       <c r="G13" t="n">
-        <v>3045.32</v>
+        <v>3298.32</v>
       </c>
       <c r="H13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -9776,10 +9555,10 @@
         <v>30</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>1880</v>
+        <v>1228.33</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>1172.21</v>
+        <v>649.23</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>188</v>
@@ -9799,13 +9578,13 @@
         <v>30</v>
       </c>
       <c r="F15" t="n">
-        <v>1636.67</v>
+        <v>1976.67</v>
       </c>
       <c r="G15" t="n">
-        <v>821.89</v>
+        <v>894.31</v>
       </c>
       <c r="H15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16">
@@ -9822,13 +9601,13 @@
         <v>30</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17">
@@ -9845,13 +9624,13 @@
         <v>30</v>
       </c>
       <c r="F17" t="n">
-        <v>258.33</v>
+        <v>283.33</v>
       </c>
       <c r="G17" t="n">
-        <v>119.69</v>
+        <v>142.84</v>
       </c>
       <c r="H17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18">
@@ -9868,13 +9647,13 @@
         <v>30</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>79.97</v>
+        <v>73.57</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>27.03</v>
+        <v>27.91</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19">
@@ -9891,13 +9670,13 @@
         <v>30</v>
       </c>
       <c r="F19" t="n">
-        <v>259.33</v>
+        <v>234.67</v>
       </c>
       <c r="G19" t="n">
-        <v>91.91</v>
+        <v>95.29</v>
       </c>
       <c r="H19" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20">
@@ -9911,16 +9690,16 @@
         <v>198</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>3.62</v>
+        <v>3.05</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.96</v>
+        <v>0.79</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21">
@@ -9934,16 +9713,16 @@
         <v>200</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>700</v>
+        <v>775</v>
       </c>
       <c r="G21" t="n">
-        <v>244.95</v>
+        <v>486.24</v>
       </c>
       <c r="H21" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22">
@@ -9960,13 +9739,13 @@
         <v>30</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>4.8</v>
+        <v>5.23</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23">
@@ -9983,13 +9762,13 @@
         <v>30</v>
       </c>
       <c r="F23" t="n">
-        <v>204.67</v>
+        <v>214.5</v>
       </c>
       <c r="G23" t="n">
-        <v>81.84</v>
+        <v>85.69</v>
       </c>
       <c r="H23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24">
@@ -10006,13 +9785,13 @@
         <v>30</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>185.33</v>
+        <v>171.5</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>56.54</v>
+        <v>49.78</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25">
@@ -10029,13 +9808,13 @@
         <v>30</v>
       </c>
       <c r="F25" t="n">
-        <v>79.83</v>
+        <v>80.83</v>
       </c>
       <c r="G25" t="n">
-        <v>37.31</v>
+        <v>37.26</v>
       </c>
       <c r="H25" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26">
@@ -10052,13 +9831,13 @@
         <v>30</v>
       </c>
       <c r="F26" t="n">
-        <v>5.43</v>
+        <v>5.53</v>
       </c>
       <c r="G26" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="H26" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -10131,22 +9910,22 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="n">
-        <v>67.6</v>
+        <v>69.63</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>13.63</v>
+        <v>14.17</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>18.77</v>
+        <v>16.2</v>
       </c>
       <c r="E6" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="F6" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="F6" s="6" t="n">
-        <v>13</v>
-      </c>
       <c r="G6" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
@@ -10159,22 +9938,22 @@
     </row>
     <row r="7">
       <c r="B7" t="n">
-        <v>63.87</v>
+        <v>64</v>
       </c>
       <c r="C7" t="n">
-        <v>15.7</v>
+        <v>17.43</v>
       </c>
       <c r="D7" t="n">
-        <v>20.43</v>
+        <v>18.57</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H7"/>
       <c r="I7"/>
@@ -10187,19 +9966,19 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="n">
-        <v>55.23</v>
+        <v>55.1</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>28.63</v>
+        <v>27.37</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>16.13</v>
+        <v>17.53</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>3</v>
@@ -10224,7 +10003,7 @@
         <v>215</v>
       </c>
       <c r="I9" t="n">
-        <v>36.7</v>
+        <v>50</v>
       </c>
       <c r="J9" t="s">
         <v>216</v>
@@ -10244,7 +10023,7 @@
         <v>217</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>36.7</v>
+        <v>23.3</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>216</v>
@@ -10362,28 +10141,28 @@
         <v>230</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>36.7</v>
+        <v>23.3</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>30</v>
+        <v>33.3</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>26.7</v>
+        <v>40</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>31.1</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="7">
@@ -10391,28 +10170,28 @@
         <v>231</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="G7" t="n">
         <v>9</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
         <v>30</v>
       </c>
-      <c r="G7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H7" t="n">
-        <v>23.3</v>
-      </c>
       <c r="I7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J7" t="n">
-        <v>31.1</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="8">
@@ -10449,16 +10228,16 @@
         <v>233</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>23.3</v>
+        <v>30</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="n">
-        <v>33.3</v>
+        <v>30</v>
       </c>
       <c r="G9" t="n">
         <v>7</v>
@@ -10467,10 +10246,10 @@
         <v>23.3</v>
       </c>
       <c r="I9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J9" t="n">
-        <v>26.7</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="10">
@@ -10478,28 +10257,28 @@
         <v>234</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>23.3</v>
+        <v>33.3</v>
       </c>
       <c r="E10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G10" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="H10" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G10" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>33.3</v>
-      </c>
       <c r="I10" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>25.6</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="11">
@@ -10507,10 +10286,10 @@
         <v>235</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>30</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="n">
         <v>8</v>
@@ -10519,16 +10298,16 @@
         <v>26.7</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H11" t="n">
-        <v>16.7</v>
+        <v>36.7</v>
       </c>
       <c r="I11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J11" t="n">
-        <v>24.4</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="12">
@@ -10536,28 +10315,28 @@
         <v>236</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" s="6" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="J12" s="6" t="n">
         <v>23.3</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="J12" s="6" t="n">
-        <v>24.4</v>
       </c>
     </row>
     <row r="13">
@@ -10565,28 +10344,28 @@
         <v>237</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F13" t="n">
-        <v>13.3</v>
+        <v>30</v>
       </c>
       <c r="G13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>23.3</v>
+        <v>20</v>
       </c>
       <c r="I13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J13" t="n">
-        <v>23.3</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="14">
@@ -10606,16 +10385,16 @@
         <v>26.7</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>23.3</v>
+        <v>20</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>23.3</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="15">
@@ -10623,22 +10402,22 @@
         <v>239</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>23.3</v>
+        <v>10</v>
       </c>
       <c r="G15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H15" t="n">
-        <v>23.3</v>
+        <v>26.7</v>
       </c>
       <c r="I15" t="n">
         <v>20</v>
@@ -10652,28 +10431,28 @@
         <v>240</v>
       </c>
       <c r="C16" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G16" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="H16" s="6" t="n">
         <v>16.7</v>
       </c>
-      <c r="E16" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>23.3</v>
-      </c>
       <c r="I16" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="J16" s="6" t="n">
         <v>20</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>22.2</v>
       </c>
     </row>
     <row r="17">
@@ -10681,28 +10460,28 @@
         <v>241</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>6.7</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F17" t="n">
-        <v>16.7</v>
+        <v>30</v>
       </c>
       <c r="G17" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>26.7</v>
+        <v>13.3</v>
       </c>
       <c r="I17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
     </row>
   </sheetData>

--- a/analysis_outputs_r/R_Analysis_Summary.xlsx
+++ b/analysis_outputs_r/R_Analysis_Summary.xlsx
@@ -1501,7 +1501,7 @@
     <t xml:space="preserve">chi-square (actor x MFS frequency)</t>
   </si>
   <si>
-    <t xml:space="preserve">chi2=2.49, df=4, p=0.6472, G-test p=0.6349, Fisher-exact p=0.6508</t>
+    <t xml:space="preserve">chi2=2.49, df=4, p=0.6472, G-test p=0.6349, Fisher-exact p=0.6526</t>
   </si>
   <si>
     <t xml:space="preserve">Cramer's V / smallest expected count</t>
